--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetSvrBussRepAssetMngProdInfo.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetSvrBussRepAssetMngProdInfo.xlsx
@@ -23,6 +23,7 @@
   <definedNames>
     <definedName name="_C01境内存款">枚举值!$B$18</definedName>
     <definedName name="_C02境外存款">枚举值!$B$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">模板!$O$1:$O$10</definedName>
     <definedName name="_R01拆借和回购">枚举值!$B$30:$P$30</definedName>
     <definedName name="_R02除回购或拆借外贷款">枚举值!$B$31</definedName>
     <definedName name="F01非金融资产">枚举值!$B$46</definedName>
@@ -4761,6 +4762,27 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4768,18 +4790,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4806,28 +4816,40 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4840,15 +4862,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4856,18 +4869,6 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -5684,7 +5685,7 @@
     <mergeCell ref="F1:AD1"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
-  <dataValidations xWindow="350" yWindow="262" count="27">
+  <dataValidations xWindow="350" yWindow="262" count="25">
     <dataValidation allowBlank="1" showErrorMessage="1" sqref="D2"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示：" prompt="请参照“输入规则”中的具体要求填写" sqref="C2"/>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D3:D65513">
@@ -5716,18 +5717,12 @@
       <formula1>0</formula1>
       <formula2>999.99999</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W4:W65527">
-      <formula1>"01 主动(自主管理),02 被动(委托管理)"</formula1>
-    </dataValidation>
     <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="预期最低收益率%必须为n(8,5)格式。" sqref="U4:U1048576">
       <formula1>0</formula1>
       <formula2>999.99999</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" promptTitle="提示" prompt="请按照输入规则具体填写" sqref="S4:S65527">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" promptTitle="提示" prompt="请按照输入规则具体填写" sqref="S1 S3:S1048576">
       <formula1>"01 是,02 否"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" promptTitle="提示" prompt="请按照输入规则具体填写" sqref="M4:M65527">
-      <formula1>"20 固定收益类,21 权益类,22 商品及金融衍生品类,23 混合类"</formula1>
     </dataValidation>
     <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="预期最高收益率%输入值必须大于等于0且必须为n(8,5)格式。" sqref="T4:T1048576">
       <formula1>0</formula1>
@@ -5749,29 +5744,29 @@
       <formula1>0</formula1>
       <formula2>999.99999</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showErrorMessage="1" promptTitle="提示" prompt="请按照输入规则具体填写" sqref="M2:M3"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G65527 AD3:AD1048576">
+    <dataValidation allowBlank="1" showErrorMessage="1" promptTitle="提示" prompt="请按照输入规则具体填写" sqref="S2"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD3:AD1048576 G1 G3:G1048576">
       <formula1>"01 是,02 否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W1">
-      <formula1>"01 主动,02 被动,99 其他"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V1 V4:V65527">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V1 V3:V1048576">
       <formula1>"01 优先,02 劣后,03 整体"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R1 R4:R65527">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R1 R3:R1048576">
       <formula1>"01 集合,02 单一,03 专项,04 定向,05 专户,99 其他"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" promptTitle="提示" prompt="请按照输入规则具体填写" sqref="M1">
-      <formula1>"01 结构性投资类,02 债券类,03 股票类,04 股权类,05 另类投资类,06 混合类,07 非标准化债权类,08 银行存款类,09 理财直接融资工具类,10 新增可投资资产类,11 代客境外投资类,12 公募基金类,13 衍生产品类,14 商品类,15 同业存单类,16 拆放同业及买入返售类"</formula1>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示" prompt="请按照输入规则具体填写" sqref="O2"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M1 M3:M1048576">
+      <formula1>"20 固定收益类,21 权益类,22 商品及金融衍生品类,23 混合类"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示" prompt="请按照输入规则具体填写" sqref="O4:O65527"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W1 W3:W1048576">
+      <formula1>"01 主动(自主管理),02 被动(委托管理),99 其他"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555596" footer="0.51180555555555596"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="350" yWindow="262" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="350" yWindow="262" count="4">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>枚举值!$A$7:$M$7</xm:f>
@@ -5789,6 +5784,12 @@
             <xm:f>各类资产应填要素列说明!$A$59:$A$64</xm:f>
           </x14:formula1>
           <xm:sqref>C1 C3:C1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示" prompt="请按照输入规则具体填写">
+          <x14:formula1>
+            <xm:f>各要素值域输入规则!$B$139:$B$234</xm:f>
+          </x14:formula1>
+          <xm:sqref>O1 O3:O1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5858,13 +5859,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="42" customHeight="1">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="71" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="90"/>
+      <c r="B1" s="72"/>
     </row>
     <row r="2" spans="1:2" ht="20.25" customHeight="1">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="83" t="s">
         <v>30</v>
       </c>
       <c r="B2" s="18" t="s">
@@ -5872,25 +5873,25 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="81"/>
+      <c r="A3" s="84"/>
       <c r="B3" s="15" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="81"/>
+      <c r="A4" s="84"/>
       <c r="B4" s="15" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="82"/>
+      <c r="A5" s="85"/>
       <c r="B5" s="13" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="6" customFormat="1">
-      <c r="A6" s="83" t="s">
+      <c r="A6" s="86" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="18" t="s">
@@ -5898,13 +5899,13 @@
       </c>
     </row>
     <row r="7" spans="1:2" s="6" customFormat="1">
-      <c r="A7" s="84"/>
+      <c r="A7" s="87"/>
       <c r="B7" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="6" customFormat="1">
-      <c r="A8" s="85" t="s">
+      <c r="A8" s="88" t="s">
         <v>38</v>
       </c>
       <c r="B8" s="11" t="s">
@@ -5912,13 +5913,13 @@
       </c>
     </row>
     <row r="9" spans="1:2" s="6" customFormat="1">
-      <c r="A9" s="84"/>
+      <c r="A9" s="87"/>
       <c r="B9" s="12" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="86" t="s">
+      <c r="A10" s="76" t="s">
         <v>41</v>
       </c>
       <c r="B10" s="15" t="s">
@@ -5926,61 +5927,61 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="87"/>
+      <c r="A11" s="89"/>
       <c r="B11" s="15" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="87"/>
+      <c r="A12" s="89"/>
       <c r="B12" s="15" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="87"/>
+      <c r="A13" s="89"/>
       <c r="B13" s="15" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="87"/>
+      <c r="A14" s="89"/>
       <c r="B14" s="15" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="87"/>
+      <c r="A15" s="89"/>
       <c r="B15" s="15" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="87"/>
+      <c r="A16" s="89"/>
       <c r="B16" s="15" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="87"/>
+      <c r="A17" s="89"/>
       <c r="B17" s="15" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="87"/>
+      <c r="A18" s="89"/>
       <c r="B18" s="15" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="87"/>
+      <c r="A19" s="89"/>
       <c r="B19" s="15" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="87"/>
+      <c r="A20" s="89"/>
       <c r="B20" s="15" t="s">
         <v>52</v>
       </c>
@@ -5994,7 +5995,7 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="86" t="s">
+      <c r="A22" s="76" t="s">
         <v>55</v>
       </c>
       <c r="B22" s="18" t="s">
@@ -6002,19 +6003,19 @@
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="87"/>
+      <c r="A23" s="89"/>
       <c r="B23" s="15" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="88"/>
+      <c r="A24" s="77"/>
       <c r="B24" s="13" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="86" t="s">
+      <c r="A25" s="76" t="s">
         <v>59</v>
       </c>
       <c r="B25" s="15" t="s">
@@ -6022,67 +6023,67 @@
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="87"/>
+      <c r="A26" s="89"/>
       <c r="B26" s="15" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="87"/>
+      <c r="A27" s="89"/>
       <c r="B27" s="10" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="87"/>
+      <c r="A28" s="89"/>
       <c r="B28" s="10" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="87"/>
+      <c r="A29" s="89"/>
       <c r="B29" s="10" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="87"/>
+      <c r="A30" s="89"/>
       <c r="B30" s="10" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="87"/>
+      <c r="A31" s="89"/>
       <c r="B31" s="10" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="87"/>
+      <c r="A32" s="89"/>
       <c r="B32" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="87"/>
+      <c r="A33" s="89"/>
       <c r="B33" s="10" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="87"/>
+      <c r="A34" s="89"/>
       <c r="B34" s="10" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="88"/>
+      <c r="A35" s="77"/>
       <c r="B35" s="30" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="86" t="s">
+      <c r="A36" s="76" t="s">
         <v>71</v>
       </c>
       <c r="B36" s="10" t="s">
@@ -6090,25 +6091,25 @@
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="87"/>
+      <c r="A37" s="89"/>
       <c r="B37" s="15" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="87"/>
+      <c r="A38" s="89"/>
       <c r="B38" s="10" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="88"/>
+      <c r="A39" s="77"/>
       <c r="B39" s="10" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="86" t="s">
+      <c r="A40" s="76" t="s">
         <v>76</v>
       </c>
       <c r="B40" s="9" t="s">
@@ -6116,43 +6117,43 @@
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="87"/>
+      <c r="A41" s="89"/>
       <c r="B41" s="10" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="87"/>
+      <c r="A42" s="89"/>
       <c r="B42" s="10" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="87"/>
+      <c r="A43" s="89"/>
       <c r="B43" s="10" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="87"/>
+      <c r="A44" s="89"/>
       <c r="B44" s="10" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="87"/>
+      <c r="A45" s="89"/>
       <c r="B45" s="10" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="88"/>
+      <c r="A46" s="77"/>
       <c r="B46" s="13" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="86" t="s">
+      <c r="A47" s="76" t="s">
         <v>84</v>
       </c>
       <c r="B47" s="18" t="s">
@@ -6160,61 +6161,61 @@
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="87"/>
+      <c r="A48" s="89"/>
       <c r="B48" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="87"/>
+      <c r="A49" s="89"/>
       <c r="B49" s="10" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="87"/>
+      <c r="A50" s="89"/>
       <c r="B50" s="10" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="87"/>
+      <c r="A51" s="89"/>
       <c r="B51" s="10" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="87"/>
+      <c r="A52" s="89"/>
       <c r="B52" s="10" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="87"/>
+      <c r="A53" s="89"/>
       <c r="B53" s="15" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="87"/>
+      <c r="A54" s="89"/>
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="87"/>
+      <c r="A55" s="89"/>
       <c r="B55" s="15" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="88"/>
+      <c r="A56" s="77"/>
       <c r="B56" s="13" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="86" t="s">
+      <c r="A57" s="76" t="s">
         <v>95</v>
       </c>
       <c r="B57" s="9" t="s">
@@ -6222,19 +6223,19 @@
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="87"/>
+      <c r="A58" s="89"/>
       <c r="B58" s="10" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="88"/>
+      <c r="A59" s="77"/>
       <c r="B59" s="13" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="86" t="s">
+      <c r="A60" s="76" t="s">
         <v>99</v>
       </c>
       <c r="B60" s="23" t="s">
@@ -6242,37 +6243,37 @@
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="87"/>
+      <c r="A61" s="89"/>
       <c r="B61" s="10" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="87"/>
+      <c r="A62" s="89"/>
       <c r="B62" s="24" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="87"/>
+      <c r="A63" s="89"/>
       <c r="B63" s="10" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="87"/>
+      <c r="A64" s="89"/>
       <c r="B64" s="10" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="88"/>
+      <c r="A65" s="77"/>
       <c r="B65" s="17" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="86" t="s">
+      <c r="A66" s="76" t="s">
         <v>106</v>
       </c>
       <c r="B66" s="23" t="s">
@@ -6280,37 +6281,37 @@
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="87"/>
+      <c r="A67" s="89"/>
       <c r="B67" s="10" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="87"/>
+      <c r="A68" s="89"/>
       <c r="B68" s="10" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="87"/>
+      <c r="A69" s="89"/>
       <c r="B69" s="10" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="87"/>
+      <c r="A70" s="89"/>
       <c r="B70" s="10" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="88"/>
+      <c r="A71" s="77"/>
       <c r="B71" s="17" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="72" spans="1:2" s="6" customFormat="1">
-      <c r="A72" s="86" t="s">
+      <c r="A72" s="76" t="s">
         <v>113</v>
       </c>
       <c r="B72" s="10" t="s">
@@ -6318,103 +6319,103 @@
       </c>
     </row>
     <row r="73" spans="1:2" s="6" customFormat="1">
-      <c r="A73" s="87"/>
+      <c r="A73" s="89"/>
       <c r="B73" s="10" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="74" spans="1:2" s="6" customFormat="1">
-      <c r="A74" s="87"/>
+      <c r="A74" s="89"/>
       <c r="B74" s="10" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:2" s="6" customFormat="1">
-      <c r="A75" s="87"/>
+      <c r="A75" s="89"/>
       <c r="B75" s="10" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="76" spans="1:2" s="6" customFormat="1">
-      <c r="A76" s="87"/>
+      <c r="A76" s="89"/>
       <c r="B76" s="10" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="77" spans="1:2" s="6" customFormat="1">
-      <c r="A77" s="87"/>
+      <c r="A77" s="89"/>
       <c r="B77" s="25" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="78" spans="1:2" s="6" customFormat="1">
-      <c r="A78" s="87"/>
+      <c r="A78" s="89"/>
       <c r="B78" s="10" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="79" spans="1:2" s="6" customFormat="1">
-      <c r="A79" s="87"/>
+      <c r="A79" s="89"/>
       <c r="B79" s="10" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="80" spans="1:2" s="6" customFormat="1">
-      <c r="A80" s="87"/>
+      <c r="A80" s="89"/>
       <c r="B80" s="10" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="81" spans="1:6" s="6" customFormat="1">
-      <c r="A81" s="87"/>
+      <c r="A81" s="89"/>
       <c r="B81" s="25" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="82" spans="1:6" s="6" customFormat="1">
-      <c r="A82" s="87"/>
+      <c r="A82" s="89"/>
       <c r="B82" s="10" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="83" spans="1:6" s="6" customFormat="1">
-      <c r="A83" s="87"/>
+      <c r="A83" s="89"/>
       <c r="B83" s="10" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="84" spans="1:6" s="6" customFormat="1">
-      <c r="A84" s="87"/>
+      <c r="A84" s="89"/>
       <c r="B84" s="10" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="85" spans="1:6" s="6" customFormat="1">
-      <c r="A85" s="87"/>
+      <c r="A85" s="89"/>
       <c r="B85" s="25" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="86" spans="1:6" s="6" customFormat="1">
-      <c r="A86" s="87"/>
+      <c r="A86" s="89"/>
       <c r="B86" s="25" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="87" spans="1:6" s="6" customFormat="1">
-      <c r="A87" s="87"/>
+      <c r="A87" s="89"/>
       <c r="B87" s="25" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="88" spans="1:6" s="6" customFormat="1">
-      <c r="A88" s="88"/>
+      <c r="A88" s="77"/>
       <c r="B88" s="13" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="89" spans="1:6" s="6" customFormat="1">
-      <c r="A89" s="86" t="s">
+      <c r="A89" s="76" t="s">
         <v>131</v>
       </c>
       <c r="B89" s="15" t="s">
@@ -6422,38 +6423,38 @@
       </c>
     </row>
     <row r="90" spans="1:6" s="6" customFormat="1">
-      <c r="A90" s="87"/>
+      <c r="A90" s="89"/>
       <c r="B90" s="15" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="91" spans="1:6" s="6" customFormat="1">
-      <c r="A91" s="87"/>
+      <c r="A91" s="89"/>
       <c r="B91" s="15" t="s">
         <v>134</v>
       </c>
       <c r="F91" s="31"/>
     </row>
     <row r="92" spans="1:6" s="6" customFormat="1">
-      <c r="A92" s="87"/>
+      <c r="A92" s="89"/>
       <c r="B92" s="32" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="93" spans="1:6" s="6" customFormat="1">
-      <c r="A93" s="87"/>
+      <c r="A93" s="89"/>
       <c r="B93" s="15" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="94" spans="1:6" s="6" customFormat="1">
-      <c r="A94" s="88"/>
+      <c r="A94" s="77"/>
       <c r="B94" s="13" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="95" spans="1:6" s="6" customFormat="1">
-      <c r="A95" s="86" t="s">
+      <c r="A95" s="76" t="s">
         <v>138</v>
       </c>
       <c r="B95" s="26" t="s">
@@ -6461,43 +6462,43 @@
       </c>
     </row>
     <row r="96" spans="1:6" s="6" customFormat="1">
-      <c r="A96" s="87"/>
+      <c r="A96" s="89"/>
       <c r="B96" s="25" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="97" spans="1:2" s="6" customFormat="1">
-      <c r="A97" s="87"/>
+      <c r="A97" s="89"/>
       <c r="B97" s="25" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="98" spans="1:2" s="6" customFormat="1">
-      <c r="A98" s="87"/>
+      <c r="A98" s="89"/>
       <c r="B98" s="25" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="99" spans="1:2" s="6" customFormat="1">
-      <c r="A99" s="87"/>
+      <c r="A99" s="89"/>
       <c r="B99" s="25" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="100" spans="1:2" s="6" customFormat="1">
-      <c r="A100" s="87"/>
+      <c r="A100" s="89"/>
       <c r="B100" s="25" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="101" spans="1:2" s="6" customFormat="1">
-      <c r="A101" s="88"/>
+      <c r="A101" s="77"/>
       <c r="B101" s="21" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="102" spans="1:2" s="6" customFormat="1">
-      <c r="A102" s="86" t="s">
+      <c r="A102" s="76" t="s">
         <v>146</v>
       </c>
       <c r="B102" s="9" t="s">
@@ -6505,7 +6506,7 @@
       </c>
     </row>
     <row r="103" spans="1:2" s="6" customFormat="1">
-      <c r="A103" s="88"/>
+      <c r="A103" s="77"/>
       <c r="B103" s="13" t="s">
         <v>148</v>
       </c>
@@ -6523,10 +6524,10 @@
       <c r="B105" s="16"/>
     </row>
     <row r="107" spans="1:2" ht="36.75" customHeight="1">
-      <c r="A107" s="89" t="s">
+      <c r="A107" s="71" t="s">
         <v>151</v>
       </c>
-      <c r="B107" s="90"/>
+      <c r="B107" s="72"/>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="36"/>
@@ -6697,17 +6698,17 @@
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="74" t="s">
+      <c r="A137" s="90" t="s">
         <v>180</v>
       </c>
-      <c r="B137" s="75"/>
+      <c r="B137" s="91"/>
     </row>
     <row r="138" spans="1:2" ht="81.75" customHeight="1">
-      <c r="A138" s="76"/>
-      <c r="B138" s="77"/>
+      <c r="A138" s="92"/>
+      <c r="B138" s="93"/>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="71" t="s">
+      <c r="A139" s="78" t="s">
         <v>181</v>
       </c>
       <c r="B139" s="38" t="s">
@@ -6715,31 +6716,31 @@
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="72"/>
+      <c r="A140" s="79"/>
       <c r="B140" s="39" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="72"/>
+      <c r="A141" s="79"/>
       <c r="B141" s="39" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="72"/>
+      <c r="A142" s="79"/>
       <c r="B142" s="39" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="73"/>
+      <c r="A143" s="80"/>
       <c r="B143" s="41" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="71" t="s">
+      <c r="A144" s="78" t="s">
         <v>187</v>
       </c>
       <c r="B144" s="38" t="s">
@@ -6747,43 +6748,43 @@
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="72"/>
+      <c r="A145" s="79"/>
       <c r="B145" s="39" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="72"/>
+      <c r="A146" s="79"/>
       <c r="B146" s="39" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="72"/>
+      <c r="A147" s="79"/>
       <c r="B147" s="39" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="72"/>
+      <c r="A148" s="79"/>
       <c r="B148" s="39" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="72"/>
+      <c r="A149" s="79"/>
       <c r="B149" s="39" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="73"/>
+      <c r="A150" s="80"/>
       <c r="B150" s="41" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="71" t="s">
+      <c r="A151" s="78" t="s">
         <v>195</v>
       </c>
       <c r="B151" s="38" t="s">
@@ -6791,187 +6792,187 @@
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="72"/>
+      <c r="A152" s="79"/>
       <c r="B152" s="39" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="72"/>
+      <c r="A153" s="79"/>
       <c r="B153" s="39" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="154" spans="1:2">
-      <c r="A154" s="72"/>
+      <c r="A154" s="79"/>
       <c r="B154" s="39" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="72"/>
+      <c r="A155" s="79"/>
       <c r="B155" s="39" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="72"/>
+      <c r="A156" s="79"/>
       <c r="B156" s="39" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="72"/>
+      <c r="A157" s="79"/>
       <c r="B157" s="39" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="72"/>
+      <c r="A158" s="79"/>
       <c r="B158" s="39" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="72"/>
+      <c r="A159" s="79"/>
       <c r="B159" s="39" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="72"/>
+      <c r="A160" s="79"/>
       <c r="B160" s="39" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="72"/>
+      <c r="A161" s="79"/>
       <c r="B161" s="39" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="72"/>
+      <c r="A162" s="79"/>
       <c r="B162" s="39" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" s="72"/>
+      <c r="A163" s="79"/>
       <c r="B163" s="39" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="72"/>
+      <c r="A164" s="79"/>
       <c r="B164" s="39" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" s="72"/>
+      <c r="A165" s="79"/>
       <c r="B165" s="39" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" s="72"/>
+      <c r="A166" s="79"/>
       <c r="B166" s="39" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="167" spans="1:2">
-      <c r="A167" s="72"/>
+      <c r="A167" s="79"/>
       <c r="B167" s="39" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="168" spans="1:2">
-      <c r="A168" s="72"/>
+      <c r="A168" s="79"/>
       <c r="B168" s="39" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="169" spans="1:2">
-      <c r="A169" s="72"/>
+      <c r="A169" s="79"/>
       <c r="B169" s="39" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="170" spans="1:2">
-      <c r="A170" s="72"/>
+      <c r="A170" s="79"/>
       <c r="B170" s="39" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="171" spans="1:2">
-      <c r="A171" s="72"/>
+      <c r="A171" s="79"/>
       <c r="B171" s="39" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="172" spans="1:2">
-      <c r="A172" s="72"/>
+      <c r="A172" s="79"/>
       <c r="B172" s="39" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="173" spans="1:2">
-      <c r="A173" s="72"/>
+      <c r="A173" s="79"/>
       <c r="B173" s="39" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="174" spans="1:2">
-      <c r="A174" s="72"/>
+      <c r="A174" s="79"/>
       <c r="B174" s="39" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="175" spans="1:2">
-      <c r="A175" s="72"/>
+      <c r="A175" s="79"/>
       <c r="B175" s="39" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="176" spans="1:2">
-      <c r="A176" s="72"/>
+      <c r="A176" s="79"/>
       <c r="B176" s="39" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="177" spans="1:2">
-      <c r="A177" s="72"/>
+      <c r="A177" s="79"/>
       <c r="B177" s="39" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="178" spans="1:2">
-      <c r="A178" s="72"/>
+      <c r="A178" s="79"/>
       <c r="B178" s="39" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="179" spans="1:2">
-      <c r="A179" s="72"/>
+      <c r="A179" s="79"/>
       <c r="B179" s="39" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="180" spans="1:2">
-      <c r="A180" s="72"/>
+      <c r="A180" s="79"/>
       <c r="B180" s="39" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="181" spans="1:2">
-      <c r="A181" s="73"/>
+      <c r="A181" s="80"/>
       <c r="B181" s="41" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="182" spans="1:2">
-      <c r="A182" s="71" t="s">
+      <c r="A182" s="78" t="s">
         <v>227</v>
       </c>
       <c r="B182" s="38" t="s">
@@ -6979,19 +6980,19 @@
       </c>
     </row>
     <row r="183" spans="1:2">
-      <c r="A183" s="72"/>
+      <c r="A183" s="79"/>
       <c r="B183" s="39" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="184" spans="1:2">
-      <c r="A184" s="73"/>
+      <c r="A184" s="80"/>
       <c r="B184" s="41" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="185" spans="1:2">
-      <c r="A185" s="71" t="s">
+      <c r="A185" s="78" t="s">
         <v>231</v>
       </c>
       <c r="B185" s="38" t="s">
@@ -6999,25 +7000,25 @@
       </c>
     </row>
     <row r="186" spans="1:2">
-      <c r="A186" s="72"/>
+      <c r="A186" s="79"/>
       <c r="B186" s="39" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="187" spans="1:2">
-      <c r="A187" s="72"/>
+      <c r="A187" s="79"/>
       <c r="B187" s="39" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="188" spans="1:2">
-      <c r="A188" s="73"/>
+      <c r="A188" s="80"/>
       <c r="B188" s="41" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="189" spans="1:2">
-      <c r="A189" s="71" t="s">
+      <c r="A189" s="78" t="s">
         <v>236</v>
       </c>
       <c r="B189" s="38" t="s">
@@ -7025,13 +7026,13 @@
       </c>
     </row>
     <row r="190" spans="1:2">
-      <c r="A190" s="73"/>
+      <c r="A190" s="80"/>
       <c r="B190" s="41" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="191" spans="1:2">
-      <c r="A191" s="71" t="s">
+      <c r="A191" s="78" t="s">
         <v>239</v>
       </c>
       <c r="B191" s="38" t="s">
@@ -7039,49 +7040,49 @@
       </c>
     </row>
     <row r="192" spans="1:2">
-      <c r="A192" s="72"/>
+      <c r="A192" s="79"/>
       <c r="B192" s="39" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="193" spans="1:2">
-      <c r="A193" s="72"/>
+      <c r="A193" s="79"/>
       <c r="B193" s="39" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="194" spans="1:2">
-      <c r="A194" s="72"/>
+      <c r="A194" s="79"/>
       <c r="B194" s="39" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="195" spans="1:2">
-      <c r="A195" s="72"/>
+      <c r="A195" s="79"/>
       <c r="B195" s="39" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="196" spans="1:2">
-      <c r="A196" s="72"/>
+      <c r="A196" s="79"/>
       <c r="B196" s="39" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="197" spans="1:2">
-      <c r="A197" s="72"/>
+      <c r="A197" s="79"/>
       <c r="B197" s="39" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="198" spans="1:2">
-      <c r="A198" s="73"/>
+      <c r="A198" s="80"/>
       <c r="B198" s="41" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="199" spans="1:2">
-      <c r="A199" s="71" t="s">
+      <c r="A199" s="78" t="s">
         <v>248</v>
       </c>
       <c r="B199" s="38" t="s">
@@ -7089,13 +7090,13 @@
       </c>
     </row>
     <row r="200" spans="1:2">
-      <c r="A200" s="73"/>
+      <c r="A200" s="80"/>
       <c r="B200" s="41" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="201" spans="1:2">
-      <c r="A201" s="71" t="s">
+      <c r="A201" s="78" t="s">
         <v>251</v>
       </c>
       <c r="B201" s="38" t="s">
@@ -7103,19 +7104,19 @@
       </c>
     </row>
     <row r="202" spans="1:2">
-      <c r="A202" s="72"/>
+      <c r="A202" s="79"/>
       <c r="B202" s="39" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="203" spans="1:2">
-      <c r="A203" s="73"/>
+      <c r="A203" s="80"/>
       <c r="B203" s="41" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="204" spans="1:2">
-      <c r="A204" s="71" t="s">
+      <c r="A204" s="78" t="s">
         <v>255</v>
       </c>
       <c r="B204" s="38" t="s">
@@ -7123,19 +7124,19 @@
       </c>
     </row>
     <row r="205" spans="1:2">
-      <c r="A205" s="72"/>
+      <c r="A205" s="79"/>
       <c r="B205" s="39" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="206" spans="1:2">
-      <c r="A206" s="72"/>
+      <c r="A206" s="79"/>
       <c r="B206" s="39" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="207" spans="1:2">
-      <c r="A207" s="73"/>
+      <c r="A207" s="80"/>
       <c r="B207" s="41" t="s">
         <v>259</v>
       </c>
@@ -7149,7 +7150,7 @@
       </c>
     </row>
     <row r="209" spans="1:2">
-      <c r="A209" s="71" t="s">
+      <c r="A209" s="78" t="s">
         <v>262</v>
       </c>
       <c r="B209" s="38" t="s">
@@ -7157,13 +7158,13 @@
       </c>
     </row>
     <row r="210" spans="1:2">
-      <c r="A210" s="73"/>
+      <c r="A210" s="80"/>
       <c r="B210" s="41" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="211" spans="1:2">
-      <c r="A211" s="71" t="s">
+      <c r="A211" s="78" t="s">
         <v>265</v>
       </c>
       <c r="B211" s="38" t="s">
@@ -7171,19 +7172,19 @@
       </c>
     </row>
     <row r="212" spans="1:2">
-      <c r="A212" s="72"/>
+      <c r="A212" s="79"/>
       <c r="B212" s="39" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="213" spans="1:2">
-      <c r="A213" s="73"/>
+      <c r="A213" s="80"/>
       <c r="B213" s="41" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="214" spans="1:2">
-      <c r="A214" s="71" t="s">
+      <c r="A214" s="78" t="s">
         <v>269</v>
       </c>
       <c r="B214" s="38" t="s">
@@ -7191,19 +7192,19 @@
       </c>
     </row>
     <row r="215" spans="1:2">
-      <c r="A215" s="72"/>
+      <c r="A215" s="79"/>
       <c r="B215" s="39" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="216" spans="1:2">
-      <c r="A216" s="73"/>
+      <c r="A216" s="80"/>
       <c r="B216" s="41" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="217" spans="1:2">
-      <c r="A217" s="71" t="s">
+      <c r="A217" s="78" t="s">
         <v>273</v>
       </c>
       <c r="B217" s="38" t="s">
@@ -7211,13 +7212,13 @@
       </c>
     </row>
     <row r="218" spans="1:2">
-      <c r="A218" s="72"/>
+      <c r="A218" s="79"/>
       <c r="B218" s="39" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="219" spans="1:2">
-      <c r="A219" s="73"/>
+      <c r="A219" s="80"/>
       <c r="B219" s="41" t="s">
         <v>276</v>
       </c>
@@ -7231,7 +7232,7 @@
       </c>
     </row>
     <row r="221" spans="1:2">
-      <c r="A221" s="71" t="s">
+      <c r="A221" s="78" t="s">
         <v>279</v>
       </c>
       <c r="B221" s="38" t="s">
@@ -7239,13 +7240,13 @@
       </c>
     </row>
     <row r="222" spans="1:2">
-      <c r="A222" s="73"/>
+      <c r="A222" s="80"/>
       <c r="B222" s="41" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="223" spans="1:2">
-      <c r="A223" s="71" t="s">
+      <c r="A223" s="78" t="s">
         <v>282</v>
       </c>
       <c r="B223" s="38" t="s">
@@ -7253,31 +7254,31 @@
       </c>
     </row>
     <row r="224" spans="1:2">
-      <c r="A224" s="72"/>
+      <c r="A224" s="79"/>
       <c r="B224" s="39" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="225" spans="1:2">
-      <c r="A225" s="72"/>
+      <c r="A225" s="79"/>
       <c r="B225" s="39" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="226" spans="1:2">
-      <c r="A226" s="72"/>
+      <c r="A226" s="79"/>
       <c r="B226" s="39" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="227" spans="1:2">
-      <c r="A227" s="73"/>
+      <c r="A227" s="80"/>
       <c r="B227" s="41" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="228" spans="1:2">
-      <c r="A228" s="71" t="s">
+      <c r="A228" s="78" t="s">
         <v>288</v>
       </c>
       <c r="B228" s="38" t="s">
@@ -7285,31 +7286,31 @@
       </c>
     </row>
     <row r="229" spans="1:2">
-      <c r="A229" s="72"/>
+      <c r="A229" s="79"/>
       <c r="B229" s="39" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="230" spans="1:2">
-      <c r="A230" s="72"/>
+      <c r="A230" s="79"/>
       <c r="B230" s="39" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="231" spans="1:2">
-      <c r="A231" s="72"/>
+      <c r="A231" s="79"/>
       <c r="B231" s="39" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="232" spans="1:2">
-      <c r="A232" s="72"/>
+      <c r="A232" s="79"/>
       <c r="B232" s="39" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="233" spans="1:2">
-      <c r="A233" s="73"/>
+      <c r="A233" s="80"/>
       <c r="B233" s="41" t="s">
         <v>294</v>
       </c>
@@ -7323,16 +7324,16 @@
       </c>
     </row>
     <row r="236" spans="1:2" ht="60" customHeight="1">
-      <c r="A236" s="91" t="s">
+      <c r="A236" s="73" t="s">
         <v>297</v>
       </c>
-      <c r="B236" s="90"/>
+      <c r="B236" s="72"/>
     </row>
     <row r="239" spans="1:2" ht="60" customHeight="1">
-      <c r="A239" s="89" t="s">
+      <c r="A239" s="71" t="s">
         <v>298</v>
       </c>
-      <c r="B239" s="90"/>
+      <c r="B239" s="72"/>
     </row>
     <row r="240" spans="1:2">
       <c r="A240" s="36"/>
@@ -7431,10 +7432,10 @@
       </c>
     </row>
     <row r="257" spans="1:2" ht="36" customHeight="1">
-      <c r="A257" s="92" t="s">
+      <c r="A257" s="74" t="s">
         <v>315</v>
       </c>
-      <c r="B257" s="93"/>
+      <c r="B257" s="75"/>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" s="36"/>
@@ -7611,10 +7612,10 @@
       </c>
     </row>
     <row r="288" spans="1:2" ht="22.5">
-      <c r="A288" s="78" t="s">
+      <c r="A288" s="81" t="s">
         <v>345</v>
       </c>
-      <c r="B288" s="79"/>
+      <c r="B288" s="82"/>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" s="44"/>
@@ -7805,6 +7806,30 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1"/>
   <mergeCells count="40">
+    <mergeCell ref="A223:A227"/>
+    <mergeCell ref="A228:A233"/>
+    <mergeCell ref="A137:B138"/>
+    <mergeCell ref="A209:A210"/>
+    <mergeCell ref="A211:A213"/>
+    <mergeCell ref="A214:A216"/>
+    <mergeCell ref="A217:A219"/>
+    <mergeCell ref="A221:A222"/>
+    <mergeCell ref="A288:B288"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A20"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A25:A35"/>
+    <mergeCell ref="A36:A39"/>
+    <mergeCell ref="A40:A46"/>
+    <mergeCell ref="A47:A56"/>
+    <mergeCell ref="A57:A59"/>
+    <mergeCell ref="A60:A65"/>
+    <mergeCell ref="A66:A71"/>
+    <mergeCell ref="A72:A88"/>
+    <mergeCell ref="A89:A94"/>
+    <mergeCell ref="A95:A101"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A107:B107"/>
     <mergeCell ref="A236:B236"/>
@@ -7821,30 +7846,6 @@
     <mergeCell ref="A199:A200"/>
     <mergeCell ref="A201:A203"/>
     <mergeCell ref="A204:A207"/>
-    <mergeCell ref="A288:B288"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A20"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="A25:A35"/>
-    <mergeCell ref="A36:A39"/>
-    <mergeCell ref="A40:A46"/>
-    <mergeCell ref="A47:A56"/>
-    <mergeCell ref="A57:A59"/>
-    <mergeCell ref="A60:A65"/>
-    <mergeCell ref="A66:A71"/>
-    <mergeCell ref="A72:A88"/>
-    <mergeCell ref="A89:A94"/>
-    <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A223:A227"/>
-    <mergeCell ref="A228:A233"/>
-    <mergeCell ref="A137:B138"/>
-    <mergeCell ref="A209:A210"/>
-    <mergeCell ref="A211:A213"/>
-    <mergeCell ref="A214:A216"/>
-    <mergeCell ref="A217:A219"/>
-    <mergeCell ref="A221:A222"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7864,10 +7865,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="36" customHeight="1">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="94" t="s">
         <v>377</v>
       </c>
-      <c r="B1" s="104"/>
+      <c r="B1" s="95"/>
     </row>
     <row r="2" spans="1:2" s="4" customFormat="1" ht="14.25">
       <c r="A2" s="7" t="s">
@@ -7881,7 +7882,7 @@
       <c r="A3" s="9" t="s">
         <v>380</v>
       </c>
-      <c r="B3" s="97" t="s">
+      <c r="B3" s="96" t="s">
         <v>1</v>
       </c>
     </row>
@@ -7889,25 +7890,25 @@
       <c r="A4" s="10" t="s">
         <v>381</v>
       </c>
-      <c r="B4" s="98"/>
+      <c r="B4" s="97"/>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="98"/>
+      <c r="B5" s="97"/>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="99"/>
+      <c r="B6" s="98"/>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="97" t="s">
+      <c r="B7" s="96" t="s">
         <v>382</v>
       </c>
     </row>
@@ -7915,25 +7916,25 @@
       <c r="A8" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="98"/>
+      <c r="B8" s="97"/>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="B9" s="98"/>
+      <c r="B9" s="97"/>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="B10" s="99"/>
+      <c r="B10" s="98"/>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="97" t="s">
+      <c r="B11" s="96" t="s">
         <v>2</v>
       </c>
     </row>
@@ -7941,85 +7942,85 @@
       <c r="A12" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="98"/>
+      <c r="B12" s="97"/>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="98"/>
+      <c r="B13" s="97"/>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="98"/>
+      <c r="B14" s="97"/>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="98"/>
+      <c r="B15" s="97"/>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="98"/>
+      <c r="B16" s="97"/>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="98"/>
+      <c r="B17" s="97"/>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="10" t="s">
         <v>383</v>
       </c>
-      <c r="B18" s="98"/>
+      <c r="B18" s="97"/>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="98"/>
+      <c r="B19" s="97"/>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="10" t="s">
         <v>384</v>
       </c>
-      <c r="B20" s="98"/>
+      <c r="B20" s="97"/>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="15" t="s">
         <v>385</v>
       </c>
-      <c r="B21" s="98"/>
+      <c r="B21" s="97"/>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="B22" s="98"/>
+      <c r="B22" s="97"/>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="105"/>
+      <c r="B23" s="99"/>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="106"/>
+      <c r="B24" s="100"/>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="B25" s="97" t="s">
+      <c r="B25" s="96" t="s">
         <v>3</v>
       </c>
     </row>
@@ -8027,61 +8028,61 @@
       <c r="A26" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B26" s="98"/>
+      <c r="B26" s="97"/>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B27" s="98"/>
+      <c r="B27" s="97"/>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B28" s="98"/>
+      <c r="B28" s="97"/>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B29" s="98"/>
+      <c r="B29" s="97"/>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="10" t="s">
         <v>387</v>
       </c>
-      <c r="B30" s="98"/>
+      <c r="B30" s="97"/>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="98"/>
+      <c r="B31" s="97"/>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="10" t="s">
         <v>388</v>
       </c>
-      <c r="B32" s="98"/>
+      <c r="B32" s="97"/>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="10" t="s">
         <v>389</v>
       </c>
-      <c r="B33" s="98"/>
+      <c r="B33" s="97"/>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="B34" s="99"/>
+      <c r="B34" s="98"/>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="18" t="s">
         <v>390</v>
       </c>
-      <c r="B35" s="97" t="s">
+      <c r="B35" s="96" t="s">
         <v>391</v>
       </c>
     </row>
@@ -8089,13 +8090,13 @@
       <c r="A36" s="17" t="s">
         <v>392</v>
       </c>
-      <c r="B36" s="99"/>
+      <c r="B36" s="98"/>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="B37" s="97" t="s">
+      <c r="B37" s="96" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8103,19 +8104,19 @@
       <c r="A38" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="B38" s="98"/>
+      <c r="B38" s="97"/>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="B39" s="98"/>
+      <c r="B39" s="97"/>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="9" t="s">
         <v>393</v>
       </c>
-      <c r="B40" s="97" t="s">
+      <c r="B40" s="96" t="s">
         <v>394</v>
       </c>
     </row>
@@ -8123,37 +8124,37 @@
       <c r="A41" s="10" t="s">
         <v>395</v>
       </c>
-      <c r="B41" s="98"/>
+      <c r="B41" s="97"/>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="B42" s="98"/>
+      <c r="B42" s="97"/>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="10" t="s">
         <v>396</v>
       </c>
-      <c r="B43" s="98"/>
+      <c r="B43" s="97"/>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="10" t="s">
         <v>397</v>
       </c>
-      <c r="B44" s="98"/>
+      <c r="B44" s="97"/>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="B45" s="98"/>
+      <c r="B45" s="97"/>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="B46" s="99"/>
+      <c r="B46" s="98"/>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="19" t="s">
@@ -8167,7 +8168,7 @@
       <c r="A48" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="B48" s="97" t="s">
+      <c r="B48" s="96" t="s">
         <v>398</v>
       </c>
     </row>
@@ -8175,13 +8176,13 @@
       <c r="A49" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="B49" s="99"/>
+      <c r="B49" s="98"/>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="B50" s="97" t="s">
+      <c r="B50" s="96" t="s">
         <v>6</v>
       </c>
     </row>
@@ -8189,25 +8190,25 @@
       <c r="A51" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="B51" s="98"/>
+      <c r="B51" s="97"/>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="B52" s="98"/>
+      <c r="B52" s="97"/>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="B53" s="98"/>
+      <c r="B53" s="97"/>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B54" s="99"/>
+      <c r="B54" s="98"/>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="19" t="s">
@@ -8221,7 +8222,7 @@
       <c r="A56" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="B56" s="97" t="s">
+      <c r="B56" s="96" t="s">
         <v>8</v>
       </c>
     </row>
@@ -8229,19 +8230,19 @@
       <c r="A57" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="B57" s="98"/>
+      <c r="B57" s="97"/>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="B58" s="99"/>
+      <c r="B58" s="98"/>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="B59" s="97" t="s">
+      <c r="B59" s="96" t="s">
         <v>7</v>
       </c>
     </row>
@@ -8249,37 +8250,37 @@
       <c r="A60" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="B60" s="98"/>
+      <c r="B60" s="97"/>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="B61" s="98"/>
+      <c r="B61" s="97"/>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="B62" s="98"/>
+      <c r="B62" s="97"/>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="B63" s="98"/>
+      <c r="B63" s="97"/>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="B64" s="99"/>
+      <c r="B64" s="98"/>
     </row>
     <row r="65" spans="1:5" ht="13.5" customHeight="1">
       <c r="A65" s="10" t="s">
         <v>401</v>
       </c>
-      <c r="B65" s="100" t="s">
+      <c r="B65" s="104" t="s">
         <v>402</v>
       </c>
     </row>
@@ -8287,26 +8288,26 @@
       <c r="A66" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B66" s="101"/>
+      <c r="B66" s="105"/>
       <c r="E66" s="22"/>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="B67" s="101"/>
+      <c r="B67" s="105"/>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="10" t="s">
         <v>403</v>
       </c>
-      <c r="B68" s="102"/>
+      <c r="B68" s="106"/>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="B69" s="97" t="s">
+      <c r="B69" s="96" t="s">
         <v>9</v>
       </c>
     </row>
@@ -8314,37 +8315,37 @@
       <c r="A70" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="B70" s="98"/>
+      <c r="B70" s="97"/>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="B71" s="98"/>
+      <c r="B71" s="97"/>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="B72" s="98"/>
+      <c r="B72" s="97"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="B73" s="98"/>
+      <c r="B73" s="97"/>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="B74" s="99"/>
+      <c r="B74" s="98"/>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="B75" s="97" t="s">
+      <c r="B75" s="96" t="s">
         <v>10</v>
       </c>
     </row>
@@ -8352,139 +8353,139 @@
       <c r="A76" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="B76" s="98"/>
+      <c r="B76" s="97"/>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="B77" s="98"/>
+      <c r="B77" s="97"/>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="B78" s="98"/>
+      <c r="B78" s="97"/>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="B79" s="98"/>
+      <c r="B79" s="97"/>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="B80" s="98"/>
+      <c r="B80" s="97"/>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="B81" s="98"/>
+      <c r="B81" s="97"/>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="B82" s="98"/>
+      <c r="B82" s="97"/>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="B83" s="98"/>
+      <c r="B83" s="97"/>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="B84" s="98"/>
+      <c r="B84" s="97"/>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="B85" s="98"/>
+      <c r="B85" s="97"/>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="B86" s="98"/>
+      <c r="B86" s="97"/>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="B87" s="98"/>
+      <c r="B87" s="97"/>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="B88" s="98"/>
+      <c r="B88" s="97"/>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="B89" s="98"/>
+      <c r="B89" s="97"/>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="B90" s="98"/>
+      <c r="B90" s="97"/>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="B91" s="98"/>
+      <c r="B91" s="97"/>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="B92" s="98"/>
+      <c r="B92" s="97"/>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="B93" s="98"/>
+      <c r="B93" s="97"/>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="25" t="s">
         <v>127</v>
       </c>
-      <c r="B94" s="98"/>
+      <c r="B94" s="97"/>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="B95" s="98"/>
+      <c r="B95" s="97"/>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="B96" s="98"/>
+      <c r="B96" s="97"/>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="B97" s="98"/>
+      <c r="B97" s="97"/>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="26" t="s">
         <v>139</v>
       </c>
-      <c r="B98" s="94" t="s">
+      <c r="B98" s="101" t="s">
         <v>11</v>
       </c>
     </row>
@@ -8492,37 +8493,37 @@
       <c r="A99" s="25" t="s">
         <v>140</v>
       </c>
-      <c r="B99" s="95"/>
+      <c r="B99" s="102"/>
     </row>
     <row r="100" spans="1:2" s="5" customFormat="1">
       <c r="A100" s="25" t="s">
         <v>141</v>
       </c>
-      <c r="B100" s="95"/>
+      <c r="B100" s="102"/>
     </row>
     <row r="101" spans="1:2" s="5" customFormat="1">
       <c r="A101" s="25" t="s">
         <v>142</v>
       </c>
-      <c r="B101" s="95"/>
+      <c r="B101" s="102"/>
     </row>
     <row r="102" spans="1:2" s="5" customFormat="1">
       <c r="A102" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="B102" s="95"/>
+      <c r="B102" s="102"/>
     </row>
     <row r="103" spans="1:2" s="5" customFormat="1">
       <c r="A103" s="25" t="s">
         <v>144</v>
       </c>
-      <c r="B103" s="95"/>
+      <c r="B103" s="102"/>
     </row>
     <row r="104" spans="1:2" s="5" customFormat="1">
       <c r="A104" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="B104" s="96"/>
+      <c r="B104" s="103"/>
     </row>
     <row r="105" spans="1:2" s="5" customFormat="1">
       <c r="A105" s="27" t="s">
@@ -8534,22 +8535,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B11:B24"/>
-    <mergeCell ref="B25:B34"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="B40:B46"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="B50:B54"/>
     <mergeCell ref="B98:B104"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="B59:B64"/>
     <mergeCell ref="B65:B68"/>
     <mergeCell ref="B69:B74"/>
     <mergeCell ref="B75:B97"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="B40:B46"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="B50:B54"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="B11:B24"/>
+    <mergeCell ref="B25:B34"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <hyperlinks>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetSvrBussRepAssetMngProdInfo.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetSvrBussRepAssetMngProdInfo.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20374"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\code\huaxia\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BS\hx\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{777FB1D4-1DA4-4A63-85BB-AB772882DBEC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28695" windowHeight="13125" tabRatio="743"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28695" windowHeight="13125" tabRatio="743" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -71,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1078" uniqueCount="932">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="933">
   <si>
     <t>公共信息（必填）</t>
   </si>
@@ -2786,9 +2787,6 @@
     <t>*购买结构</t>
   </si>
   <si>
-    <t>*管理方式</t>
-  </si>
-  <si>
     <t>*管理费率%</t>
   </si>
   <si>
@@ -4089,18 +4087,26 @@
   </si>
   <si>
     <t>ZWE 津巴布韦</t>
+  </si>
+  <si>
+    <t>*是否掌控计划底层资产详情</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>*管理方式</t>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.00_ "/>
     <numFmt numFmtId="177" formatCode="0.00000_ "/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -4762,27 +4768,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4790,6 +4775,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4816,40 +4813,28 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4862,6 +4847,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4870,11 +4864,23 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
-    <cellStyle name="Normal_G10revised-20050118" xfId="1"/>
+    <cellStyle name="Normal_G10revised-20050118" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="4"/>
+    <cellStyle name="常规 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="超链接" xfId="3" builtinId="8"/>
     <cellStyle name="千位分隔" xfId="2" builtinId="3"/>
   </cellStyles>
@@ -5219,9 +5225,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AH10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.75" style="50" customWidth="1"/>
     <col min="2" max="2" width="15.375" style="50"/>
@@ -5245,18 +5251,20 @@
     <col min="20" max="20" width="17.125" style="61" customWidth="1"/>
     <col min="21" max="21" width="16.5" style="61" customWidth="1"/>
     <col min="22" max="22" width="12.75" style="50" customWidth="1"/>
-    <col min="23" max="23" width="12.875" style="50" customWidth="1"/>
-    <col min="24" max="25" width="14.25" style="61" customWidth="1"/>
-    <col min="26" max="26" width="21" style="61" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="25.5" style="61" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="17.875" style="61" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="16.5" style="51" customWidth="1"/>
-    <col min="30" max="30" width="51.875" style="50" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="19.25" style="52" customWidth="1"/>
-    <col min="33" max="33" width="21" style="52" customWidth="1"/>
+    <col min="23" max="23" width="10.875" style="50" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="28.625" style="50" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.125" style="61" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.25" style="61" customWidth="1"/>
+    <col min="27" max="27" width="21" style="61" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="25.5" style="61" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="17.875" style="61" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.5" style="51" customWidth="1"/>
+    <col min="31" max="31" width="51.875" style="50" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="19.25" style="52" customWidth="1"/>
+    <col min="34" max="34" width="21" style="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" s="47" customFormat="1" ht="14.25" thickBot="1">
+    <row r="1" spans="1:34" s="47" customFormat="1" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
@@ -5291,13 +5299,14 @@
       <c r="AB1" s="70"/>
       <c r="AC1" s="70"/>
       <c r="AD1" s="70"/>
-      <c r="AE1" s="69" t="s">
+      <c r="AE1" s="70"/>
+      <c r="AF1" s="69" t="s">
         <v>405</v>
       </c>
-      <c r="AF1" s="69"/>
       <c r="AG1" s="69"/>
-    </row>
-    <row r="2" spans="1:33" s="48" customFormat="1">
+      <c r="AH1" s="69"/>
+    </row>
+    <row r="2" spans="1:34" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A2" s="53" t="s">
         <v>13</v>
       </c>
@@ -5365,40 +5374,43 @@
         <v>507</v>
       </c>
       <c r="W2" s="62" t="s">
+        <v>932</v>
+      </c>
+      <c r="X2" s="62" t="s">
+        <v>931</v>
+      </c>
+      <c r="Y2" s="62" t="s">
         <v>508</v>
       </c>
-      <c r="X2" s="62" t="s">
+      <c r="Z2" s="62" t="s">
         <v>509</v>
       </c>
-      <c r="Y2" s="62" t="s">
+      <c r="AA2" s="62" t="s">
         <v>510</v>
       </c>
-      <c r="Z2" s="62" t="s">
+      <c r="AB2" s="62" t="s">
         <v>511</v>
       </c>
-      <c r="AA2" s="62" t="s">
+      <c r="AC2" s="62" t="s">
         <v>512</v>
       </c>
-      <c r="AB2" s="62" t="s">
+      <c r="AD2" s="55" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE2" s="54" t="s">
         <v>513</v>
       </c>
-      <c r="AC2" s="55" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD2" s="54" t="s">
-        <v>514</v>
-      </c>
-      <c r="AE2" s="56" t="s">
+      <c r="AF2" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="AF2" s="56" t="s">
+      <c r="AG2" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="AG2" s="56" t="s">
+      <c r="AH2" s="56" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:33" s="49" customFormat="1">
+    <row r="3" spans="1:34" s="49" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A3" s="50"/>
       <c r="B3" s="50"/>
       <c r="C3" s="50"/>
@@ -5422,18 +5434,19 @@
       <c r="U3" s="65"/>
       <c r="V3" s="63"/>
       <c r="W3" s="63"/>
-      <c r="X3" s="65"/>
+      <c r="X3" s="63"/>
       <c r="Y3" s="65"/>
       <c r="Z3" s="65"/>
       <c r="AA3" s="65"/>
       <c r="AB3" s="65"/>
-      <c r="AC3" s="51"/>
-      <c r="AD3" s="50"/>
-      <c r="AE3" s="52"/>
+      <c r="AC3" s="65"/>
+      <c r="AD3" s="51"/>
+      <c r="AE3" s="50"/>
       <c r="AF3" s="52"/>
       <c r="AG3" s="52"/>
-    </row>
-    <row r="4" spans="1:33" s="49" customFormat="1">
+      <c r="AH3" s="52"/>
+    </row>
+    <row r="4" spans="1:34" s="49" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A4" s="50"/>
       <c r="B4" s="50"/>
       <c r="C4" s="50"/>
@@ -5457,18 +5470,19 @@
       <c r="U4" s="65"/>
       <c r="V4" s="63"/>
       <c r="W4" s="63"/>
-      <c r="X4" s="65"/>
+      <c r="X4" s="63"/>
       <c r="Y4" s="65"/>
       <c r="Z4" s="65"/>
       <c r="AA4" s="65"/>
       <c r="AB4" s="65"/>
-      <c r="AC4" s="51"/>
-      <c r="AD4" s="50"/>
-      <c r="AE4" s="52"/>
+      <c r="AC4" s="65"/>
+      <c r="AD4" s="51"/>
+      <c r="AE4" s="50"/>
       <c r="AF4" s="52"/>
       <c r="AG4" s="52"/>
-    </row>
-    <row r="5" spans="1:33" s="49" customFormat="1">
+      <c r="AH4" s="52"/>
+    </row>
+    <row r="5" spans="1:34" s="49" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A5" s="50"/>
       <c r="B5" s="50"/>
       <c r="C5" s="50"/>
@@ -5492,18 +5506,19 @@
       <c r="U5" s="61"/>
       <c r="V5" s="50"/>
       <c r="W5" s="50"/>
-      <c r="X5" s="61"/>
+      <c r="X5" s="50"/>
       <c r="Y5" s="61"/>
       <c r="Z5" s="61"/>
       <c r="AA5" s="61"/>
       <c r="AB5" s="61"/>
-      <c r="AC5" s="51"/>
-      <c r="AD5" s="50"/>
-      <c r="AE5" s="52"/>
+      <c r="AC5" s="61"/>
+      <c r="AD5" s="51"/>
+      <c r="AE5" s="50"/>
       <c r="AF5" s="52"/>
       <c r="AG5" s="52"/>
-    </row>
-    <row r="6" spans="1:33" s="49" customFormat="1">
+      <c r="AH5" s="52"/>
+    </row>
+    <row r="6" spans="1:34" s="49" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A6" s="50"/>
       <c r="B6" s="50"/>
       <c r="C6" s="50"/>
@@ -5527,18 +5542,19 @@
       <c r="U6" s="61"/>
       <c r="V6" s="50"/>
       <c r="W6" s="50"/>
-      <c r="X6" s="61"/>
+      <c r="X6" s="50"/>
       <c r="Y6" s="61"/>
       <c r="Z6" s="61"/>
       <c r="AA6" s="61"/>
       <c r="AB6" s="61"/>
-      <c r="AC6" s="51"/>
-      <c r="AD6" s="50"/>
-      <c r="AE6" s="52"/>
+      <c r="AC6" s="61"/>
+      <c r="AD6" s="51"/>
+      <c r="AE6" s="50"/>
       <c r="AF6" s="52"/>
       <c r="AG6" s="52"/>
-    </row>
-    <row r="7" spans="1:33" s="49" customFormat="1">
+      <c r="AH6" s="52"/>
+    </row>
+    <row r="7" spans="1:34" s="49" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A7" s="50"/>
       <c r="B7" s="50"/>
       <c r="C7" s="50"/>
@@ -5562,18 +5578,19 @@
       <c r="U7" s="61"/>
       <c r="V7" s="50"/>
       <c r="W7" s="50"/>
-      <c r="X7" s="61"/>
+      <c r="X7" s="50"/>
       <c r="Y7" s="61"/>
       <c r="Z7" s="61"/>
       <c r="AA7" s="61"/>
       <c r="AB7" s="61"/>
-      <c r="AC7" s="51"/>
-      <c r="AD7" s="50"/>
-      <c r="AE7" s="52"/>
+      <c r="AC7" s="61"/>
+      <c r="AD7" s="51"/>
+      <c r="AE7" s="50"/>
       <c r="AF7" s="52"/>
       <c r="AG7" s="52"/>
-    </row>
-    <row r="8" spans="1:33" s="49" customFormat="1">
+      <c r="AH7" s="52"/>
+    </row>
+    <row r="8" spans="1:34" s="49" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A8" s="50"/>
       <c r="B8" s="50"/>
       <c r="C8" s="50"/>
@@ -5597,18 +5614,19 @@
       <c r="U8" s="61"/>
       <c r="V8" s="50"/>
       <c r="W8" s="50"/>
-      <c r="X8" s="61"/>
+      <c r="X8" s="50"/>
       <c r="Y8" s="61"/>
       <c r="Z8" s="61"/>
       <c r="AA8" s="61"/>
       <c r="AB8" s="61"/>
-      <c r="AC8" s="51"/>
-      <c r="AD8" s="50"/>
-      <c r="AE8" s="52"/>
+      <c r="AC8" s="61"/>
+      <c r="AD8" s="51"/>
+      <c r="AE8" s="50"/>
       <c r="AF8" s="52"/>
       <c r="AG8" s="52"/>
-    </row>
-    <row r="9" spans="1:33" s="49" customFormat="1">
+      <c r="AH8" s="52"/>
+    </row>
+    <row r="9" spans="1:34" s="49" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A9" s="50"/>
       <c r="B9" s="50"/>
       <c r="C9" s="50"/>
@@ -5632,18 +5650,19 @@
       <c r="U9" s="61"/>
       <c r="V9" s="50"/>
       <c r="W9" s="50"/>
-      <c r="X9" s="61"/>
+      <c r="X9" s="50"/>
       <c r="Y9" s="61"/>
       <c r="Z9" s="61"/>
       <c r="AA9" s="61"/>
       <c r="AB9" s="61"/>
-      <c r="AC9" s="51"/>
-      <c r="AD9" s="50"/>
-      <c r="AE9" s="52"/>
+      <c r="AC9" s="61"/>
+      <c r="AD9" s="51"/>
+      <c r="AE9" s="50"/>
       <c r="AF9" s="52"/>
       <c r="AG9" s="52"/>
-    </row>
-    <row r="10" spans="1:33" s="49" customFormat="1">
+      <c r="AH9" s="52"/>
+    </row>
+    <row r="10" spans="1:34" s="49" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A10" s="50"/>
       <c r="B10" s="50"/>
       <c r="C10" s="50"/>
@@ -5667,99 +5686,100 @@
       <c r="U10" s="61"/>
       <c r="V10" s="50"/>
       <c r="W10" s="50"/>
-      <c r="X10" s="61"/>
+      <c r="X10" s="50"/>
       <c r="Y10" s="61"/>
       <c r="Z10" s="61"/>
       <c r="AA10" s="61"/>
       <c r="AB10" s="61"/>
-      <c r="AC10" s="51"/>
-      <c r="AD10" s="50"/>
-      <c r="AE10" s="52"/>
+      <c r="AC10" s="61"/>
+      <c r="AD10" s="51"/>
+      <c r="AE10" s="50"/>
       <c r="AF10" s="52"/>
       <c r="AG10" s="52"/>
+      <c r="AH10" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="AE1:AG1"/>
-    <mergeCell ref="F1:AD1"/>
+    <mergeCell ref="AF1:AH1"/>
+    <mergeCell ref="F1:AE1"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <dataValidations xWindow="350" yWindow="262" count="25">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="D2"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示：" prompt="请参照“输入规则”中的具体要求填写" sqref="C2"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D3:D65513">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="D2" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示：" prompt="请参照“输入规则”中的具体要求填写" sqref="C2" xr:uid="{00000000-0002-0000-0000-000001000000}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D3:D65513" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"01 银行间债券市场,02 商业银行柜台市场,03 上海证券交易所,04 深圳证券交易所,05 全国中小企业股份转让系统,06 上海期货交易所,07 郑州商品交易所,08 大连商品交易所,09 中国金融期货交易所,10 上海黄金交易所,11 区域性产权/资产交易市场,12 区域性商品交易所,13 区域性贵金属交易所,14 艺术品市场,15 基金市场,16 信托市场,17 全国银行间同业拆借市场,18 上海票据交易所,99 其他交易流通场所"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF3:AF1048576">
-      <formula1>INDIRECT($AE$3)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG3:AG1048576" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>INDIRECT($AF$3)</formula1>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="其他合计费率%输入值必须大于等于0且必须为n(8,5)格式。" sqref="AB4:AB1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH3" xr:uid="{00000000-0002-0000-0000-000004000000}">
+      <formula1>INDIRECT($AG$3)</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="其他合计费率%输入值必须大于等于0且必须为n(8,5)格式。" sqref="AC4:AC1048576" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>0</formula1>
       <formula2>999.99999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="中介服务机构合计费率%输入值必须大于等于0且必须为n(8,5)格式。" sqref="AA4:AA1048576">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="中介服务机构合计费率%输入值必须大于等于0且必须为n(8,5)格式。" sqref="AB4:AB1048576" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>0</formula1>
       <formula2>999.99999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="交易相关合计费率%输入值必须大于等于0且必须为n(8,5)格式。" sqref="Z4:Z1048576">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="交易相关合计费率%输入值必须大于等于0且必须为n(8,5)格式。" sqref="AA4:AA1048576" xr:uid="{00000000-0002-0000-0000-000007000000}">
       <formula1>0</formula1>
       <formula2>999.99999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="托管费率%输入值必须大于等于0且必须为n(8,5)格式。" sqref="Y4:Y1048576">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="托管费率%输入值必须大于等于0且必须为n(8,5)格式。" sqref="Z4:Z1048576" xr:uid="{00000000-0002-0000-0000-000008000000}">
       <formula1>0</formula1>
       <formula2>999.99999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="管理费率%输入值必须大于等于0且必须为n(8,5)格式。" sqref="X4:X1048576">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="管理费率%输入值必须大于等于0且必须为n(8,5)格式。" sqref="Y4:Y1048576" xr:uid="{00000000-0002-0000-0000-000009000000}">
       <formula1>0</formula1>
       <formula2>999.99999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="预期最低收益率%必须为n(8,5)格式。" sqref="U4:U1048576">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="预期最低收益率%必须为n(8,5)格式。" sqref="U4:U1048576" xr:uid="{00000000-0002-0000-0000-00000A000000}">
       <formula1>0</formula1>
       <formula2>999.99999</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" promptTitle="提示" prompt="请按照输入规则具体填写" sqref="S1 S3:S1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" promptTitle="提示" prompt="请按照输入规则具体填写" sqref="S1 S3:S1048576" xr:uid="{00000000-0002-0000-0000-00000B000000}">
       <formula1>"01 是,02 否"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="预期最高收益率%输入值必须大于等于0且必须为n(8,5)格式。" sqref="T4:T1048576">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="预期最高收益率%输入值必须大于等于0且必须为n(8,5)格式。" sqref="T4:T1048576" xr:uid="{00000000-0002-0000-0000-00000C000000}">
       <formula1>0</formula1>
       <formula2>999.99999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="金额输入值必须大于等于0且必须为n(15,2)格式。" sqref="L4:L1048576">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="金额输入值必须大于等于0且必须为n(15,2)格式。" sqref="L4:L1048576" xr:uid="{00000000-0002-0000-0000-00000D000000}">
       <formula1>0</formula1>
       <formula2>9999999999999.99</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值整数位不可超过3位，小数位不可超过5位" sqref="U1:U3">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值整数位不可超过3位，小数位不可超过5位" sqref="U1:U3" xr:uid="{00000000-0002-0000-0000-00000E000000}">
       <formula1>0</formula1>
       <formula2>999.99999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值不能为负，整数位不可超过13位，小数位不可超过2位" sqref="L1:L3">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值不能为负，整数位不可超过13位，小数位不可超过2位" sqref="L1:L3" xr:uid="{00000000-0002-0000-0000-00000F000000}">
       <formula1>0</formula1>
       <formula2>9999999999999.99</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值不能为负，整数位不可超过3位，小数位不可超过5位" sqref="T1:T3 X1:AB3">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值不能为负，整数位不可超过3位，小数位不可超过5位" sqref="T1:T3 Y1:AC3" xr:uid="{00000000-0002-0000-0000-000010000000}">
       <formula1>0</formula1>
       <formula2>999.99999</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showErrorMessage="1" promptTitle="提示" prompt="请按照输入规则具体填写" sqref="S2"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD3:AD1048576 G1 G3:G1048576">
+    <dataValidation allowBlank="1" showErrorMessage="1" promptTitle="提示" prompt="请按照输入规则具体填写" sqref="S2" xr:uid="{00000000-0002-0000-0000-000011000000}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE3:AE1048576 G1 G3:G1048576 X3:X1048576" xr:uid="{00000000-0002-0000-0000-000012000000}">
       <formula1>"01 是,02 否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V1 V3:V1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V1 V3:V1048576" xr:uid="{00000000-0002-0000-0000-000013000000}">
       <formula1>"01 优先,02 劣后,03 整体"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R1 R3:R1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R1 R3:R1048576" xr:uid="{00000000-0002-0000-0000-000014000000}">
       <formula1>"01 集合,02 单一,03 专项,04 定向,05 专户,99 其他"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示" prompt="请按照输入规则具体填写" sqref="O2"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M1 M3:M1048576">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示" prompt="请按照输入规则具体填写" sqref="O2" xr:uid="{00000000-0002-0000-0000-000015000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE2" xr:uid="{00000000-0002-0000-0000-000016000000}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M1 M3:M1048576" xr:uid="{00000000-0002-0000-0000-000017000000}">
       <formula1>"20 固定收益类,21 权益类,22 商品及金融衍生品类,23 混合类"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W1 W3:W1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W1:X1 W3:W1048576" xr:uid="{00000000-0002-0000-0000-000018000000}">
       <formula1>"01 主动(自主管理),02 被动(委托管理),99 其他"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5767,25 +5787,25 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="350" yWindow="262" count="4">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000019000000}">
           <x14:formula1>
             <xm:f>枚举值!$A$7:$M$7</xm:f>
           </x14:formula1>
-          <xm:sqref>AE3:AE1048576</xm:sqref>
+          <xm:sqref>AF3:AF1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00001A000000}">
           <x14:formula1>
             <xm:f>币种填写规则!$A$1:$A$178</xm:f>
           </x14:formula1>
           <xm:sqref>E1 E3:E1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示：" prompt="请参照“输入规则”中的具体要求填写">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示：" prompt="请参照“输入规则”中的具体要求填写" xr:uid="{00000000-0002-0000-0000-00001B000000}">
           <x14:formula1>
             <xm:f>各类资产应填要素列说明!$A$59:$A$64</xm:f>
           </x14:formula1>
           <xm:sqref>C1 C3:C1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示" prompt="请按照输入规则具体填写">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示" prompt="请按照输入规则具体填写" xr:uid="{00000000-0002-0000-0000-00001C000000}">
           <x14:formula1>
             <xm:f>各要素值域输入规则!$B$139:$B$234</xm:f>
           </x14:formula1>
@@ -5798,45 +5818,45 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="95.125" style="1" customWidth="1"/>
     <col min="2" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="24" customHeight="1">
+    <row r="1" spans="1:1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="46" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="38.25" customHeight="1">
+    <row r="2" spans="1:1" ht="38.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="45" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="24.75" customHeight="1">
+    <row r="3" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="45" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="35.25" customHeight="1">
+    <row r="4" spans="1:1" ht="35.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="45" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="39" customHeight="1">
+    <row r="5" spans="1:1" ht="39" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="45" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:1" s="45" customFormat="1" ht="36.75" customHeight="1">
+    <row r="6" spans="1:1" s="45" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="45" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="24.75" customHeight="1">
+    <row r="7" spans="1:1" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="45" t="s">
         <v>28</v>
       </c>
@@ -5848,9 +5868,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:IV319"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="32.25" style="6" customWidth="1"/>
     <col min="2" max="2" width="44.75" style="6" customWidth="1"/>
@@ -5858,135 +5878,135 @@
     <col min="257" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="42" customHeight="1">
-      <c r="A1" s="71" t="s">
+    <row r="1" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="89" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="72"/>
-    </row>
-    <row r="2" spans="1:2" ht="20.25" customHeight="1">
-      <c r="A2" s="83" t="s">
+      <c r="B1" s="90"/>
+    </row>
+    <row r="2" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="80" t="s">
         <v>30</v>
       </c>
       <c r="B2" s="18" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="84"/>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A3" s="81"/>
       <c r="B3" s="15" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="84"/>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A4" s="81"/>
       <c r="B4" s="15" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="85"/>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A5" s="82"/>
       <c r="B5" s="13" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:2" s="6" customFormat="1">
-      <c r="A6" s="86" t="s">
+    <row r="6" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="83" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="18" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:2" s="6" customFormat="1">
-      <c r="A7" s="87"/>
+    <row r="7" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="84"/>
       <c r="B7" s="12" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:2" s="6" customFormat="1">
-      <c r="A8" s="88" t="s">
+    <row r="8" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="85" t="s">
         <v>38</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:2" s="6" customFormat="1">
-      <c r="A9" s="87"/>
+    <row r="9" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="84"/>
       <c r="B9" s="12" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="76" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A10" s="86" t="s">
         <v>41</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="89"/>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A11" s="87"/>
       <c r="B11" s="15" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="89"/>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A12" s="87"/>
       <c r="B12" s="15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="89"/>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A13" s="87"/>
       <c r="B13" s="15" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="89"/>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A14" s="87"/>
       <c r="B14" s="15" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="89"/>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A15" s="87"/>
       <c r="B15" s="15" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="89"/>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A16" s="87"/>
       <c r="B16" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="89"/>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A17" s="87"/>
       <c r="B17" s="15" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="89"/>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A18" s="87"/>
       <c r="B18" s="15" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="89"/>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A19" s="87"/>
       <c r="B19" s="15" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="89"/>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A20" s="87"/>
       <c r="B20" s="15" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A21" s="29" t="s">
         <v>53</v>
       </c>
@@ -5994,524 +6014,524 @@
         <v>54</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="76" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A22" s="86" t="s">
         <v>55</v>
       </c>
       <c r="B22" s="18" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="89"/>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A23" s="87"/>
       <c r="B23" s="15" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="77"/>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A24" s="88"/>
       <c r="B24" s="13" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="76" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A25" s="86" t="s">
         <v>59</v>
       </c>
       <c r="B25" s="15" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="89"/>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A26" s="87"/>
       <c r="B26" s="15" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="89"/>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A27" s="87"/>
       <c r="B27" s="10" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="89"/>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A28" s="87"/>
       <c r="B28" s="10" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="89"/>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A29" s="87"/>
       <c r="B29" s="10" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="89"/>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A30" s="87"/>
       <c r="B30" s="10" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="89"/>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A31" s="87"/>
       <c r="B31" s="10" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="89"/>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A32" s="87"/>
       <c r="B32" s="10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="89"/>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A33" s="87"/>
       <c r="B33" s="10" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="89"/>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A34" s="87"/>
       <c r="B34" s="10" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="77"/>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A35" s="88"/>
       <c r="B35" s="30" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="76" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A36" s="86" t="s">
         <v>71</v>
       </c>
       <c r="B36" s="10" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="89"/>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A37" s="87"/>
       <c r="B37" s="15" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="89"/>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A38" s="87"/>
       <c r="B38" s="10" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="77"/>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A39" s="88"/>
       <c r="B39" s="10" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="76" t="s">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A40" s="86" t="s">
         <v>76</v>
       </c>
       <c r="B40" s="9" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="89"/>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A41" s="87"/>
       <c r="B41" s="10" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="89"/>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A42" s="87"/>
       <c r="B42" s="10" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
-      <c r="A43" s="89"/>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A43" s="87"/>
       <c r="B43" s="10" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
-      <c r="A44" s="89"/>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A44" s="87"/>
       <c r="B44" s="10" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
-      <c r="A45" s="89"/>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A45" s="87"/>
       <c r="B45" s="10" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
-      <c r="A46" s="77"/>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A46" s="88"/>
       <c r="B46" s="13" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
-      <c r="A47" s="76" t="s">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A47" s="86" t="s">
         <v>84</v>
       </c>
       <c r="B47" s="18" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
-      <c r="A48" s="89"/>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A48" s="87"/>
       <c r="B48" s="10" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
-      <c r="A49" s="89"/>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A49" s="87"/>
       <c r="B49" s="10" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
-      <c r="A50" s="89"/>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A50" s="87"/>
       <c r="B50" s="10" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
-      <c r="A51" s="89"/>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A51" s="87"/>
       <c r="B51" s="10" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
-      <c r="A52" s="89"/>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A52" s="87"/>
       <c r="B52" s="10" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
-      <c r="A53" s="89"/>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A53" s="87"/>
       <c r="B53" s="15" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
-      <c r="A54" s="89"/>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A54" s="87"/>
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
-      <c r="A55" s="89"/>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A55" s="87"/>
       <c r="B55" s="15" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
-      <c r="A56" s="77"/>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A56" s="88"/>
       <c r="B56" s="13" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
-      <c r="A57" s="76" t="s">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A57" s="86" t="s">
         <v>95</v>
       </c>
       <c r="B57" s="9" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
-      <c r="A58" s="89"/>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A58" s="87"/>
       <c r="B58" s="10" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
-      <c r="A59" s="77"/>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A59" s="88"/>
       <c r="B59" s="13" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
-      <c r="A60" s="76" t="s">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A60" s="86" t="s">
         <v>99</v>
       </c>
       <c r="B60" s="23" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
-      <c r="A61" s="89"/>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A61" s="87"/>
       <c r="B61" s="10" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
-      <c r="A62" s="89"/>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A62" s="87"/>
       <c r="B62" s="24" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
-      <c r="A63" s="89"/>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A63" s="87"/>
       <c r="B63" s="10" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
-      <c r="A64" s="89"/>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A64" s="87"/>
       <c r="B64" s="10" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
-      <c r="A65" s="77"/>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A65" s="88"/>
       <c r="B65" s="17" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
-      <c r="A66" s="76" t="s">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A66" s="86" t="s">
         <v>106</v>
       </c>
       <c r="B66" s="23" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
-      <c r="A67" s="89"/>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A67" s="87"/>
       <c r="B67" s="10" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
-      <c r="A68" s="89"/>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A68" s="87"/>
       <c r="B68" s="10" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
-      <c r="A69" s="89"/>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A69" s="87"/>
       <c r="B69" s="10" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
-      <c r="A70" s="89"/>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A70" s="87"/>
       <c r="B70" s="10" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
-      <c r="A71" s="77"/>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A71" s="88"/>
       <c r="B71" s="17" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="72" spans="1:2" s="6" customFormat="1">
-      <c r="A72" s="76" t="s">
+    <row r="72" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A72" s="86" t="s">
         <v>113</v>
       </c>
       <c r="B72" s="10" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="73" spans="1:2" s="6" customFormat="1">
-      <c r="A73" s="89"/>
+    <row r="73" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A73" s="87"/>
       <c r="B73" s="10" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="74" spans="1:2" s="6" customFormat="1">
-      <c r="A74" s="89"/>
+    <row r="74" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A74" s="87"/>
       <c r="B74" s="10" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="75" spans="1:2" s="6" customFormat="1">
-      <c r="A75" s="89"/>
+    <row r="75" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A75" s="87"/>
       <c r="B75" s="10" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="76" spans="1:2" s="6" customFormat="1">
-      <c r="A76" s="89"/>
+    <row r="76" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A76" s="87"/>
       <c r="B76" s="10" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="77" spans="1:2" s="6" customFormat="1">
-      <c r="A77" s="89"/>
+    <row r="77" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A77" s="87"/>
       <c r="B77" s="25" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="78" spans="1:2" s="6" customFormat="1">
-      <c r="A78" s="89"/>
+    <row r="78" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A78" s="87"/>
       <c r="B78" s="10" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="79" spans="1:2" s="6" customFormat="1">
-      <c r="A79" s="89"/>
+    <row r="79" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A79" s="87"/>
       <c r="B79" s="10" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="80" spans="1:2" s="6" customFormat="1">
-      <c r="A80" s="89"/>
+    <row r="80" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A80" s="87"/>
       <c r="B80" s="10" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="81" spans="1:6" s="6" customFormat="1">
-      <c r="A81" s="89"/>
+    <row r="81" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A81" s="87"/>
       <c r="B81" s="25" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="82" spans="1:6" s="6" customFormat="1">
-      <c r="A82" s="89"/>
+    <row r="82" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A82" s="87"/>
       <c r="B82" s="10" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="83" spans="1:6" s="6" customFormat="1">
-      <c r="A83" s="89"/>
+    <row r="83" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A83" s="87"/>
       <c r="B83" s="10" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="84" spans="1:6" s="6" customFormat="1">
-      <c r="A84" s="89"/>
+    <row r="84" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A84" s="87"/>
       <c r="B84" s="10" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="85" spans="1:6" s="6" customFormat="1">
-      <c r="A85" s="89"/>
+    <row r="85" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A85" s="87"/>
       <c r="B85" s="25" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="86" spans="1:6" s="6" customFormat="1">
-      <c r="A86" s="89"/>
+    <row r="86" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A86" s="87"/>
       <c r="B86" s="25" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="87" spans="1:6" s="6" customFormat="1">
-      <c r="A87" s="89"/>
+    <row r="87" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A87" s="87"/>
       <c r="B87" s="25" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="88" spans="1:6" s="6" customFormat="1">
-      <c r="A88" s="77"/>
+    <row r="88" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A88" s="88"/>
       <c r="B88" s="13" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="89" spans="1:6" s="6" customFormat="1">
-      <c r="A89" s="76" t="s">
+    <row r="89" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A89" s="86" t="s">
         <v>131</v>
       </c>
       <c r="B89" s="15" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="90" spans="1:6" s="6" customFormat="1">
-      <c r="A90" s="89"/>
+    <row r="90" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A90" s="87"/>
       <c r="B90" s="15" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="91" spans="1:6" s="6" customFormat="1">
-      <c r="A91" s="89"/>
+    <row r="91" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A91" s="87"/>
       <c r="B91" s="15" t="s">
         <v>134</v>
       </c>
       <c r="F91" s="31"/>
     </row>
-    <row r="92" spans="1:6" s="6" customFormat="1">
-      <c r="A92" s="89"/>
+    <row r="92" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A92" s="87"/>
       <c r="B92" s="32" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="93" spans="1:6" s="6" customFormat="1">
-      <c r="A93" s="89"/>
+    <row r="93" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A93" s="87"/>
       <c r="B93" s="15" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="94" spans="1:6" s="6" customFormat="1">
-      <c r="A94" s="77"/>
+    <row r="94" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A94" s="88"/>
       <c r="B94" s="13" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="95" spans="1:6" s="6" customFormat="1">
-      <c r="A95" s="76" t="s">
+    <row r="95" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A95" s="86" t="s">
         <v>138</v>
       </c>
       <c r="B95" s="26" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="96" spans="1:6" s="6" customFormat="1">
-      <c r="A96" s="89"/>
+    <row r="96" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A96" s="87"/>
       <c r="B96" s="25" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="97" spans="1:2" s="6" customFormat="1">
-      <c r="A97" s="89"/>
+    <row r="97" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A97" s="87"/>
       <c r="B97" s="25" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="98" spans="1:2" s="6" customFormat="1">
-      <c r="A98" s="89"/>
+    <row r="98" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A98" s="87"/>
       <c r="B98" s="25" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="99" spans="1:2" s="6" customFormat="1">
-      <c r="A99" s="89"/>
+    <row r="99" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A99" s="87"/>
       <c r="B99" s="25" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="100" spans="1:2" s="6" customFormat="1">
-      <c r="A100" s="89"/>
+    <row r="100" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A100" s="87"/>
       <c r="B100" s="25" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="101" spans="1:2" s="6" customFormat="1">
-      <c r="A101" s="77"/>
+    <row r="101" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A101" s="88"/>
       <c r="B101" s="21" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="102" spans="1:2" s="6" customFormat="1">
-      <c r="A102" s="76" t="s">
+    <row r="102" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A102" s="86" t="s">
         <v>146</v>
       </c>
       <c r="B102" s="9" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="103" spans="1:2" s="6" customFormat="1">
-      <c r="A103" s="77"/>
+    <row r="103" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A103" s="88"/>
       <c r="B103" s="13" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="104" spans="1:2">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A104" s="33" t="s">
         <v>149</v>
       </c>
@@ -6519,629 +6539,629 @@
         <v>150</v>
       </c>
     </row>
-    <row r="105" spans="1:2">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A105" s="35"/>
       <c r="B105" s="16"/>
     </row>
-    <row r="107" spans="1:2" ht="36.75" customHeight="1">
-      <c r="A107" s="71" t="s">
+    <row r="107" spans="1:2" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A107" s="89" t="s">
         <v>151</v>
       </c>
-      <c r="B107" s="72"/>
-    </row>
-    <row r="108" spans="1:2">
+      <c r="B107" s="90"/>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A108" s="36"/>
       <c r="B108" s="10" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="109" spans="1:2">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A109" s="36"/>
       <c r="B109" s="10" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="110" spans="1:2">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A110" s="36"/>
       <c r="B110" s="10" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="111" spans="1:2">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A111" s="36"/>
       <c r="B111" s="10" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="112" spans="1:2">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A112" s="36"/>
       <c r="B112" s="10" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="113" spans="1:2">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A113" s="36"/>
       <c r="B113" s="10" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="114" spans="1:2">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A114" s="36"/>
       <c r="B114" s="10" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="115" spans="1:2">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A115" s="36"/>
       <c r="B115" s="10" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="116" spans="1:2">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A116" s="36"/>
       <c r="B116" s="10" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="117" spans="1:2">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A117" s="36"/>
       <c r="B117" s="10" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="118" spans="1:2">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A118" s="36"/>
       <c r="B118" s="10" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="119" spans="1:2">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A119" s="36"/>
       <c r="B119" s="10" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="120" spans="1:2">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A120" s="36"/>
       <c r="B120" s="10" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="121" spans="1:2">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A121" s="36"/>
       <c r="B121" s="10" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="122" spans="1:2">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A122" s="36"/>
       <c r="B122" s="10" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="123" spans="1:2">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A123" s="36"/>
       <c r="B123" s="10" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="124" spans="1:2">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A124" s="36"/>
       <c r="B124" s="10" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="125" spans="1:2">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A125" s="36"/>
       <c r="B125" s="10" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="126" spans="1:2">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A126" s="36"/>
       <c r="B126" s="10" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="127" spans="1:2">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A127" s="36"/>
       <c r="B127" s="10" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="128" spans="1:2">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A128" s="36"/>
       <c r="B128" s="10" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="129" spans="1:2">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A129" s="36"/>
       <c r="B129" s="10" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="130" spans="1:2">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A130" s="36"/>
       <c r="B130" s="10" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="131" spans="1:2">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A131" s="36"/>
       <c r="B131" s="10" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="132" spans="1:2">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A132" s="36"/>
       <c r="B132" s="10" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="133" spans="1:2">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A133" s="36"/>
       <c r="B133" s="10" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="134" spans="1:2">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A134" s="36"/>
       <c r="B134" s="10" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="135" spans="1:2">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A135" s="37"/>
       <c r="B135" s="17" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="137" spans="1:2">
-      <c r="A137" s="90" t="s">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A137" s="74" t="s">
         <v>180</v>
       </c>
-      <c r="B137" s="91"/>
-    </row>
-    <row r="138" spans="1:2" ht="81.75" customHeight="1">
-      <c r="A138" s="92"/>
-      <c r="B138" s="93"/>
-    </row>
-    <row r="139" spans="1:2">
-      <c r="A139" s="78" t="s">
+      <c r="B137" s="75"/>
+    </row>
+    <row r="138" spans="1:2" ht="81.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A138" s="76"/>
+      <c r="B138" s="77"/>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A139" s="71" t="s">
         <v>181</v>
       </c>
       <c r="B139" s="38" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="140" spans="1:2">
-      <c r="A140" s="79"/>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A140" s="72"/>
       <c r="B140" s="39" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="141" spans="1:2">
-      <c r="A141" s="79"/>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A141" s="72"/>
       <c r="B141" s="39" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="142" spans="1:2">
-      <c r="A142" s="79"/>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A142" s="72"/>
       <c r="B142" s="39" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="143" spans="1:2">
-      <c r="A143" s="80"/>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A143" s="73"/>
       <c r="B143" s="41" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="144" spans="1:2">
-      <c r="A144" s="78" t="s">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A144" s="71" t="s">
         <v>187</v>
       </c>
       <c r="B144" s="38" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="145" spans="1:2">
-      <c r="A145" s="79"/>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A145" s="72"/>
       <c r="B145" s="39" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="146" spans="1:2">
-      <c r="A146" s="79"/>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A146" s="72"/>
       <c r="B146" s="39" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="147" spans="1:2">
-      <c r="A147" s="79"/>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A147" s="72"/>
       <c r="B147" s="39" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="148" spans="1:2">
-      <c r="A148" s="79"/>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A148" s="72"/>
       <c r="B148" s="39" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="149" spans="1:2">
-      <c r="A149" s="79"/>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A149" s="72"/>
       <c r="B149" s="39" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="150" spans="1:2">
-      <c r="A150" s="80"/>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A150" s="73"/>
       <c r="B150" s="41" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="151" spans="1:2">
-      <c r="A151" s="78" t="s">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A151" s="71" t="s">
         <v>195</v>
       </c>
       <c r="B151" s="38" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="152" spans="1:2">
-      <c r="A152" s="79"/>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A152" s="72"/>
       <c r="B152" s="39" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="153" spans="1:2">
-      <c r="A153" s="79"/>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A153" s="72"/>
       <c r="B153" s="39" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="154" spans="1:2">
-      <c r="A154" s="79"/>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A154" s="72"/>
       <c r="B154" s="39" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="155" spans="1:2">
-      <c r="A155" s="79"/>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A155" s="72"/>
       <c r="B155" s="39" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="156" spans="1:2">
-      <c r="A156" s="79"/>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A156" s="72"/>
       <c r="B156" s="39" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="157" spans="1:2">
-      <c r="A157" s="79"/>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A157" s="72"/>
       <c r="B157" s="39" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="158" spans="1:2">
-      <c r="A158" s="79"/>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A158" s="72"/>
       <c r="B158" s="39" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="159" spans="1:2">
-      <c r="A159" s="79"/>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A159" s="72"/>
       <c r="B159" s="39" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="160" spans="1:2">
-      <c r="A160" s="79"/>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A160" s="72"/>
       <c r="B160" s="39" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="161" spans="1:2">
-      <c r="A161" s="79"/>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A161" s="72"/>
       <c r="B161" s="39" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="162" spans="1:2">
-      <c r="A162" s="79"/>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A162" s="72"/>
       <c r="B162" s="39" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="163" spans="1:2">
-      <c r="A163" s="79"/>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A163" s="72"/>
       <c r="B163" s="39" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="164" spans="1:2">
-      <c r="A164" s="79"/>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A164" s="72"/>
       <c r="B164" s="39" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="165" spans="1:2">
-      <c r="A165" s="79"/>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A165" s="72"/>
       <c r="B165" s="39" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="166" spans="1:2">
-      <c r="A166" s="79"/>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A166" s="72"/>
       <c r="B166" s="39" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="167" spans="1:2">
-      <c r="A167" s="79"/>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A167" s="72"/>
       <c r="B167" s="39" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="168" spans="1:2">
-      <c r="A168" s="79"/>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A168" s="72"/>
       <c r="B168" s="39" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="169" spans="1:2">
-      <c r="A169" s="79"/>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A169" s="72"/>
       <c r="B169" s="39" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="170" spans="1:2">
-      <c r="A170" s="79"/>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A170" s="72"/>
       <c r="B170" s="39" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="171" spans="1:2">
-      <c r="A171" s="79"/>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A171" s="72"/>
       <c r="B171" s="39" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="172" spans="1:2">
-      <c r="A172" s="79"/>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A172" s="72"/>
       <c r="B172" s="39" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="173" spans="1:2">
-      <c r="A173" s="79"/>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A173" s="72"/>
       <c r="B173" s="39" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="174" spans="1:2">
-      <c r="A174" s="79"/>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A174" s="72"/>
       <c r="B174" s="39" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="175" spans="1:2">
-      <c r="A175" s="79"/>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A175" s="72"/>
       <c r="B175" s="39" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="176" spans="1:2">
-      <c r="A176" s="79"/>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A176" s="72"/>
       <c r="B176" s="39" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="177" spans="1:2">
-      <c r="A177" s="79"/>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A177" s="72"/>
       <c r="B177" s="39" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="178" spans="1:2">
-      <c r="A178" s="79"/>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A178" s="72"/>
       <c r="B178" s="39" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="179" spans="1:2">
-      <c r="A179" s="79"/>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A179" s="72"/>
       <c r="B179" s="39" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="180" spans="1:2">
-      <c r="A180" s="79"/>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A180" s="72"/>
       <c r="B180" s="39" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="181" spans="1:2">
-      <c r="A181" s="80"/>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A181" s="73"/>
       <c r="B181" s="41" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="182" spans="1:2">
-      <c r="A182" s="78" t="s">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A182" s="71" t="s">
         <v>227</v>
       </c>
       <c r="B182" s="38" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="183" spans="1:2">
-      <c r="A183" s="79"/>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A183" s="72"/>
       <c r="B183" s="39" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="184" spans="1:2">
-      <c r="A184" s="80"/>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A184" s="73"/>
       <c r="B184" s="41" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="185" spans="1:2">
-      <c r="A185" s="78" t="s">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A185" s="71" t="s">
         <v>231</v>
       </c>
       <c r="B185" s="38" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="186" spans="1:2">
-      <c r="A186" s="79"/>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A186" s="72"/>
       <c r="B186" s="39" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="187" spans="1:2">
-      <c r="A187" s="79"/>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A187" s="72"/>
       <c r="B187" s="39" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="188" spans="1:2">
-      <c r="A188" s="80"/>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A188" s="73"/>
       <c r="B188" s="41" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="189" spans="1:2">
-      <c r="A189" s="78" t="s">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A189" s="71" t="s">
         <v>236</v>
       </c>
       <c r="B189" s="38" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="190" spans="1:2">
-      <c r="A190" s="80"/>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A190" s="73"/>
       <c r="B190" s="41" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="191" spans="1:2">
-      <c r="A191" s="78" t="s">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A191" s="71" t="s">
         <v>239</v>
       </c>
       <c r="B191" s="38" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="192" spans="1:2">
-      <c r="A192" s="79"/>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A192" s="72"/>
       <c r="B192" s="39" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="193" spans="1:2">
-      <c r="A193" s="79"/>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A193" s="72"/>
       <c r="B193" s="39" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="194" spans="1:2">
-      <c r="A194" s="79"/>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A194" s="72"/>
       <c r="B194" s="39" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="195" spans="1:2">
-      <c r="A195" s="79"/>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A195" s="72"/>
       <c r="B195" s="39" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="196" spans="1:2">
-      <c r="A196" s="79"/>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A196" s="72"/>
       <c r="B196" s="39" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="197" spans="1:2">
-      <c r="A197" s="79"/>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A197" s="72"/>
       <c r="B197" s="39" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="198" spans="1:2">
-      <c r="A198" s="80"/>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A198" s="73"/>
       <c r="B198" s="41" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="199" spans="1:2">
-      <c r="A199" s="78" t="s">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A199" s="71" t="s">
         <v>248</v>
       </c>
       <c r="B199" s="38" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="200" spans="1:2">
-      <c r="A200" s="80"/>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A200" s="73"/>
       <c r="B200" s="41" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="201" spans="1:2">
-      <c r="A201" s="78" t="s">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A201" s="71" t="s">
         <v>251</v>
       </c>
       <c r="B201" s="38" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="202" spans="1:2">
-      <c r="A202" s="79"/>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A202" s="72"/>
       <c r="B202" s="39" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="203" spans="1:2">
-      <c r="A203" s="80"/>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A203" s="73"/>
       <c r="B203" s="41" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="204" spans="1:2">
-      <c r="A204" s="78" t="s">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A204" s="71" t="s">
         <v>255</v>
       </c>
       <c r="B204" s="38" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="205" spans="1:2">
-      <c r="A205" s="79"/>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A205" s="72"/>
       <c r="B205" s="39" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="206" spans="1:2">
-      <c r="A206" s="79"/>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A206" s="72"/>
       <c r="B206" s="39" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="207" spans="1:2">
-      <c r="A207" s="80"/>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A207" s="73"/>
       <c r="B207" s="41" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="208" spans="1:2">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A208" s="42" t="s">
         <v>260</v>
       </c>
@@ -7149,81 +7169,81 @@
         <v>261</v>
       </c>
     </row>
-    <row r="209" spans="1:2">
-      <c r="A209" s="78" t="s">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A209" s="71" t="s">
         <v>262</v>
       </c>
       <c r="B209" s="38" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="210" spans="1:2">
-      <c r="A210" s="80"/>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A210" s="73"/>
       <c r="B210" s="41" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="211" spans="1:2">
-      <c r="A211" s="78" t="s">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A211" s="71" t="s">
         <v>265</v>
       </c>
       <c r="B211" s="38" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="212" spans="1:2">
-      <c r="A212" s="79"/>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A212" s="72"/>
       <c r="B212" s="39" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="213" spans="1:2">
-      <c r="A213" s="80"/>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A213" s="73"/>
       <c r="B213" s="41" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="214" spans="1:2">
-      <c r="A214" s="78" t="s">
+    <row r="214" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A214" s="71" t="s">
         <v>269</v>
       </c>
       <c r="B214" s="38" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="215" spans="1:2">
-      <c r="A215" s="79"/>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A215" s="72"/>
       <c r="B215" s="39" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="216" spans="1:2">
-      <c r="A216" s="80"/>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A216" s="73"/>
       <c r="B216" s="41" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="217" spans="1:2">
-      <c r="A217" s="78" t="s">
+    <row r="217" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A217" s="71" t="s">
         <v>273</v>
       </c>
       <c r="B217" s="38" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="218" spans="1:2">
-      <c r="A218" s="79"/>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A218" s="72"/>
       <c r="B218" s="39" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="219" spans="1:2">
-      <c r="A219" s="80"/>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A219" s="73"/>
       <c r="B219" s="41" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="220" spans="1:2">
+    <row r="220" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A220" s="42" t="s">
         <v>277</v>
       </c>
@@ -7231,91 +7251,91 @@
         <v>278</v>
       </c>
     </row>
-    <row r="221" spans="1:2">
-      <c r="A221" s="78" t="s">
+    <row r="221" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A221" s="71" t="s">
         <v>279</v>
       </c>
       <c r="B221" s="38" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="222" spans="1:2">
-      <c r="A222" s="80"/>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A222" s="73"/>
       <c r="B222" s="41" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="223" spans="1:2">
-      <c r="A223" s="78" t="s">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A223" s="71" t="s">
         <v>282</v>
       </c>
       <c r="B223" s="38" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="224" spans="1:2">
-      <c r="A224" s="79"/>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A224" s="72"/>
       <c r="B224" s="39" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="225" spans="1:2">
-      <c r="A225" s="79"/>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A225" s="72"/>
       <c r="B225" s="39" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="226" spans="1:2">
-      <c r="A226" s="79"/>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A226" s="72"/>
       <c r="B226" s="39" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="227" spans="1:2">
-      <c r="A227" s="80"/>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A227" s="73"/>
       <c r="B227" s="41" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="228" spans="1:2">
-      <c r="A228" s="78" t="s">
+    <row r="228" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A228" s="71" t="s">
         <v>288</v>
       </c>
       <c r="B228" s="38" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="229" spans="1:2">
-      <c r="A229" s="79"/>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A229" s="72"/>
       <c r="B229" s="39" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="230" spans="1:2">
-      <c r="A230" s="79"/>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A230" s="72"/>
       <c r="B230" s="39" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="231" spans="1:2">
-      <c r="A231" s="79"/>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A231" s="72"/>
       <c r="B231" s="39" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="232" spans="1:2">
-      <c r="A232" s="79"/>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A232" s="72"/>
       <c r="B232" s="39" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="233" spans="1:2">
-      <c r="A233" s="80"/>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A233" s="73"/>
       <c r="B233" s="41" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="234" spans="1:2">
+    <row r="234" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A234" s="40" t="s">
         <v>295</v>
       </c>
@@ -7323,481 +7343,481 @@
         <v>296</v>
       </c>
     </row>
-    <row r="236" spans="1:2" ht="60" customHeight="1">
-      <c r="A236" s="73" t="s">
+    <row r="236" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A236" s="91" t="s">
         <v>297</v>
       </c>
-      <c r="B236" s="72"/>
-    </row>
-    <row r="239" spans="1:2" ht="60" customHeight="1">
-      <c r="A239" s="71" t="s">
+      <c r="B236" s="90"/>
+    </row>
+    <row r="239" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A239" s="89" t="s">
         <v>298</v>
       </c>
-      <c r="B239" s="72"/>
-    </row>
-    <row r="240" spans="1:2">
+      <c r="B239" s="90"/>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A240" s="36"/>
       <c r="B240" s="39" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="241" spans="1:2">
+    <row r="241" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A241" s="36"/>
       <c r="B241" s="39" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="242" spans="1:2">
+    <row r="242" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A242" s="36"/>
       <c r="B242" s="39" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="243" spans="1:2">
+    <row r="243" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A243" s="36"/>
       <c r="B243" s="39" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="244" spans="1:2">
+    <row r="244" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A244" s="36"/>
       <c r="B244" s="39" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="245" spans="1:2">
+    <row r="245" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A245" s="36"/>
       <c r="B245" s="39" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="246" spans="1:2">
+    <row r="246" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A246" s="36"/>
       <c r="B246" s="39" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="247" spans="1:2">
+    <row r="247" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A247" s="36"/>
       <c r="B247" s="39" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="248" spans="1:2">
+    <row r="248" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A248" s="36"/>
       <c r="B248" s="39" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="249" spans="1:2">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A249" s="36"/>
       <c r="B249" s="39" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="250" spans="1:2">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A250" s="36"/>
       <c r="B250" s="39" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="251" spans="1:2">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A251" s="36"/>
       <c r="B251" s="39" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="252" spans="1:2">
+    <row r="252" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A252" s="36"/>
       <c r="B252" s="39" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="253" spans="1:2">
+    <row r="253" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A253" s="36"/>
       <c r="B253" s="39" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="254" spans="1:2">
+    <row r="254" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A254" s="36"/>
       <c r="B254" s="39" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="255" spans="1:2">
+    <row r="255" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A255" s="37"/>
       <c r="B255" s="41" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="257" spans="1:2" ht="36" customHeight="1">
-      <c r="A257" s="74" t="s">
+    <row r="257" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A257" s="92" t="s">
         <v>315</v>
       </c>
-      <c r="B257" s="75"/>
-    </row>
-    <row r="258" spans="1:2">
+      <c r="B257" s="93"/>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A258" s="36"/>
       <c r="B258" s="39" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="259" spans="1:2">
+    <row r="259" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A259" s="36"/>
       <c r="B259" s="39" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="260" spans="1:2">
+    <row r="260" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A260" s="36"/>
       <c r="B260" s="39" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="261" spans="1:2">
+    <row r="261" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A261" s="36"/>
       <c r="B261" s="39" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="262" spans="1:2">
+    <row r="262" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A262" s="36"/>
       <c r="B262" s="39" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="263" spans="1:2">
+    <row r="263" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A263" s="36"/>
       <c r="B263" s="39" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="264" spans="1:2">
+    <row r="264" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A264" s="36"/>
       <c r="B264" s="39" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="265" spans="1:2">
+    <row r="265" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A265" s="36"/>
       <c r="B265" s="39" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="266" spans="1:2">
+    <row r="266" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A266" s="36"/>
       <c r="B266" s="39" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="267" spans="1:2">
+    <row r="267" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A267" s="36"/>
       <c r="B267" s="39" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="268" spans="1:2">
+    <row r="268" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A268" s="36"/>
       <c r="B268" s="39" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="269" spans="1:2">
+    <row r="269" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A269" s="36"/>
       <c r="B269" s="39" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="270" spans="1:2">
+    <row r="270" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A270" s="36"/>
       <c r="B270" s="39" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="271" spans="1:2">
+    <row r="271" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A271" s="36"/>
       <c r="B271" s="39" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="272" spans="1:2">
+    <row r="272" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A272" s="36"/>
       <c r="B272" s="39" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="273" spans="1:2">
+    <row r="273" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A273" s="36"/>
       <c r="B273" s="39" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="274" spans="1:2">
+    <row r="274" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A274" s="36"/>
       <c r="B274" s="39" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="275" spans="1:2">
+    <row r="275" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A275" s="36"/>
       <c r="B275" s="39" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="276" spans="1:2">
+    <row r="276" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A276" s="36"/>
       <c r="B276" s="39" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="277" spans="1:2">
+    <row r="277" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A277" s="36"/>
       <c r="B277" s="39" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="278" spans="1:2">
+    <row r="278" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A278" s="36"/>
       <c r="B278" s="39" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="279" spans="1:2">
+    <row r="279" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A279" s="36"/>
       <c r="B279" s="39" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="280" spans="1:2">
+    <row r="280" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A280" s="36"/>
       <c r="B280" s="39" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="281" spans="1:2">
+    <row r="281" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A281" s="36"/>
       <c r="B281" s="39" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="282" spans="1:2">
+    <row r="282" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A282" s="36"/>
       <c r="B282" s="39" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="283" spans="1:2">
+    <row r="283" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A283" s="36"/>
       <c r="B283" s="39" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="284" spans="1:2">
+    <row r="284" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A284" s="36"/>
       <c r="B284" s="39" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="285" spans="1:2">
+    <row r="285" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A285" s="36"/>
       <c r="B285" s="39" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="286" spans="1:2">
+    <row r="286" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A286" s="37"/>
       <c r="B286" s="41" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="288" spans="1:2" ht="22.5">
-      <c r="A288" s="81" t="s">
+    <row r="288" spans="1:2" ht="22.5" x14ac:dyDescent="0.15">
+      <c r="A288" s="78" t="s">
         <v>345</v>
       </c>
-      <c r="B288" s="82"/>
-    </row>
-    <row r="289" spans="1:2">
+      <c r="B288" s="79"/>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A289" s="44"/>
       <c r="B289" s="38" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="290" spans="1:2">
+    <row r="290" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A290" s="36"/>
       <c r="B290" s="39" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="291" spans="1:2">
+    <row r="291" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A291" s="36"/>
       <c r="B291" s="39" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="292" spans="1:2">
+    <row r="292" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A292" s="36"/>
       <c r="B292" s="39" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="293" spans="1:2">
+    <row r="293" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A293" s="36"/>
       <c r="B293" s="39" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="294" spans="1:2">
+    <row r="294" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A294" s="36"/>
       <c r="B294" s="39" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="295" spans="1:2">
+    <row r="295" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A295" s="36"/>
       <c r="B295" s="39" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="296" spans="1:2">
+    <row r="296" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A296" s="36"/>
       <c r="B296" s="57" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="297" spans="1:2">
+    <row r="297" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A297" s="36"/>
       <c r="B297" s="57" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="298" spans="1:2">
+    <row r="298" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A298" s="36"/>
       <c r="B298" s="39" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="299" spans="1:2">
+    <row r="299" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A299" s="36"/>
       <c r="B299" s="39" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="300" spans="1:2">
+    <row r="300" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A300" s="36"/>
       <c r="B300" s="39" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="301" spans="1:2">
+    <row r="301" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A301" s="36"/>
       <c r="B301" s="39" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="302" spans="1:2">
+    <row r="302" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A302" s="36"/>
       <c r="B302" s="39" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="303" spans="1:2">
+    <row r="303" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A303" s="36"/>
       <c r="B303" s="39" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="304" spans="1:2">
+    <row r="304" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A304" s="36"/>
       <c r="B304" s="39" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="305" spans="1:2">
+    <row r="305" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A305" s="36"/>
       <c r="B305" s="39" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="306" spans="1:2">
+    <row r="306" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A306" s="36"/>
       <c r="B306" s="39" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="307" spans="1:2">
+    <row r="307" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A307" s="36"/>
       <c r="B307" s="39" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="308" spans="1:2">
+    <row r="308" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A308" s="36"/>
       <c r="B308" s="39" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="309" spans="1:2">
+    <row r="309" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A309" s="36"/>
       <c r="B309" s="39" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="310" spans="1:2">
+    <row r="310" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A310" s="36"/>
       <c r="B310" s="39" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="311" spans="1:2">
+    <row r="311" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A311" s="36"/>
       <c r="B311" s="39" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="312" spans="1:2">
+    <row r="312" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A312" s="36"/>
       <c r="B312" s="39" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="313" spans="1:2">
+    <row r="313" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A313" s="36"/>
       <c r="B313" s="39" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="314" spans="1:2">
+    <row r="314" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A314" s="36"/>
       <c r="B314" s="39" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="315" spans="1:2">
+    <row r="315" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A315" s="36"/>
       <c r="B315" s="39" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="316" spans="1:2">
+    <row r="316" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A316" s="36"/>
       <c r="B316" s="39" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="317" spans="1:2">
+    <row r="317" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A317" s="36"/>
       <c r="B317" s="39" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="318" spans="1:2">
+    <row r="318" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A318" s="36"/>
       <c r="B318" s="39" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="319" spans="1:2">
+    <row r="319" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A319" s="37"/>
       <c r="B319" s="41" t="s">
         <v>376</v>
@@ -7806,14 +7826,22 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1"/>
   <mergeCells count="40">
-    <mergeCell ref="A223:A227"/>
-    <mergeCell ref="A228:A233"/>
-    <mergeCell ref="A137:B138"/>
-    <mergeCell ref="A209:A210"/>
-    <mergeCell ref="A211:A213"/>
-    <mergeCell ref="A214:A216"/>
-    <mergeCell ref="A217:A219"/>
-    <mergeCell ref="A221:A222"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A107:B107"/>
+    <mergeCell ref="A236:B236"/>
+    <mergeCell ref="A239:B239"/>
+    <mergeCell ref="A257:B257"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="A139:A143"/>
+    <mergeCell ref="A144:A150"/>
+    <mergeCell ref="A151:A181"/>
+    <mergeCell ref="A182:A184"/>
+    <mergeCell ref="A185:A188"/>
+    <mergeCell ref="A189:A190"/>
+    <mergeCell ref="A191:A198"/>
+    <mergeCell ref="A199:A200"/>
+    <mergeCell ref="A201:A203"/>
+    <mergeCell ref="A204:A207"/>
     <mergeCell ref="A288:B288"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A6:A7"/>
@@ -7830,22 +7858,14 @@
     <mergeCell ref="A72:A88"/>
     <mergeCell ref="A89:A94"/>
     <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A107:B107"/>
-    <mergeCell ref="A236:B236"/>
-    <mergeCell ref="A239:B239"/>
-    <mergeCell ref="A257:B257"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="A139:A143"/>
-    <mergeCell ref="A144:A150"/>
-    <mergeCell ref="A151:A181"/>
-    <mergeCell ref="A182:A184"/>
-    <mergeCell ref="A185:A188"/>
-    <mergeCell ref="A189:A190"/>
-    <mergeCell ref="A191:A198"/>
-    <mergeCell ref="A199:A200"/>
-    <mergeCell ref="A201:A203"/>
-    <mergeCell ref="A204:A207"/>
+    <mergeCell ref="A223:A227"/>
+    <mergeCell ref="A228:A233"/>
+    <mergeCell ref="A137:B138"/>
+    <mergeCell ref="A209:A210"/>
+    <mergeCell ref="A211:A213"/>
+    <mergeCell ref="A214:A216"/>
+    <mergeCell ref="A217:A219"/>
+    <mergeCell ref="A221:A222"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7854,9 +7874,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:IV105"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="38.125" style="6" customWidth="1"/>
     <col min="2" max="2" width="76.625" style="6" customWidth="1"/>
@@ -7864,13 +7884,13 @@
     <col min="257" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="36" customHeight="1">
-      <c r="A1" s="94" t="s">
+    <row r="1" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="103" t="s">
         <v>377</v>
       </c>
-      <c r="B1" s="95"/>
-    </row>
-    <row r="2" spans="1:2" s="4" customFormat="1" ht="14.25">
+      <c r="B1" s="104"/>
+    </row>
+    <row r="2" spans="1:2" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A2" s="7" t="s">
         <v>378</v>
       </c>
@@ -7878,285 +7898,285 @@
         <v>379</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A3" s="9" t="s">
         <v>380</v>
       </c>
-      <c r="B3" s="96" t="s">
+      <c r="B3" s="97" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A4" s="10" t="s">
         <v>381</v>
       </c>
-      <c r="B4" s="97"/>
-    </row>
-    <row r="5" spans="1:2">
+      <c r="B4" s="98"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A5" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="97"/>
-    </row>
-    <row r="6" spans="1:2">
+      <c r="B5" s="98"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A6" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="98"/>
-    </row>
-    <row r="7" spans="1:2">
+      <c r="B6" s="99"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A7" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="96" t="s">
+      <c r="B7" s="97" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A8" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="97"/>
-    </row>
-    <row r="9" spans="1:2">
+      <c r="B8" s="98"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A9" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="B9" s="97"/>
-    </row>
-    <row r="10" spans="1:2">
+      <c r="B9" s="98"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A10" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="B10" s="98"/>
-    </row>
-    <row r="11" spans="1:2">
+      <c r="B10" s="99"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A11" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="96" t="s">
+      <c r="B11" s="97" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A12" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="97"/>
-    </row>
-    <row r="13" spans="1:2">
+      <c r="B12" s="98"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A13" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="97"/>
-    </row>
-    <row r="14" spans="1:2">
+      <c r="B13" s="98"/>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A14" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="97"/>
-    </row>
-    <row r="15" spans="1:2">
+      <c r="B14" s="98"/>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A15" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="97"/>
-    </row>
-    <row r="16" spans="1:2">
+      <c r="B15" s="98"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A16" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="97"/>
-    </row>
-    <row r="17" spans="1:2">
+      <c r="B16" s="98"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A17" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="97"/>
-    </row>
-    <row r="18" spans="1:2">
+      <c r="B17" s="98"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A18" s="10" t="s">
         <v>383</v>
       </c>
-      <c r="B18" s="97"/>
-    </row>
-    <row r="19" spans="1:2">
+      <c r="B18" s="98"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A19" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="97"/>
-    </row>
-    <row r="20" spans="1:2">
+      <c r="B19" s="98"/>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A20" s="10" t="s">
         <v>384</v>
       </c>
-      <c r="B20" s="97"/>
-    </row>
-    <row r="21" spans="1:2">
+      <c r="B20" s="98"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A21" s="15" t="s">
         <v>385</v>
       </c>
-      <c r="B21" s="97"/>
-    </row>
-    <row r="22" spans="1:2">
+      <c r="B21" s="98"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A22" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="B22" s="97"/>
-    </row>
-    <row r="23" spans="1:2">
+      <c r="B22" s="98"/>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A23" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="99"/>
-    </row>
-    <row r="24" spans="1:2">
+      <c r="B23" s="105"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A24" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="100"/>
-    </row>
-    <row r="25" spans="1:2">
+      <c r="B24" s="106"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A25" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="B25" s="96" t="s">
+      <c r="B25" s="97" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A26" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B26" s="97"/>
-    </row>
-    <row r="27" spans="1:2">
+      <c r="B26" s="98"/>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A27" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B27" s="97"/>
-    </row>
-    <row r="28" spans="1:2">
+      <c r="B27" s="98"/>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A28" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B28" s="97"/>
-    </row>
-    <row r="29" spans="1:2">
+      <c r="B28" s="98"/>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A29" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B29" s="97"/>
-    </row>
-    <row r="30" spans="1:2">
+      <c r="B29" s="98"/>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A30" s="10" t="s">
         <v>387</v>
       </c>
-      <c r="B30" s="97"/>
-    </row>
-    <row r="31" spans="1:2">
+      <c r="B30" s="98"/>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A31" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="97"/>
-    </row>
-    <row r="32" spans="1:2">
+      <c r="B31" s="98"/>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A32" s="10" t="s">
         <v>388</v>
       </c>
-      <c r="B32" s="97"/>
-    </row>
-    <row r="33" spans="1:2">
+      <c r="B32" s="98"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A33" s="10" t="s">
         <v>389</v>
       </c>
-      <c r="B33" s="97"/>
-    </row>
-    <row r="34" spans="1:2">
+      <c r="B33" s="98"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A34" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="B34" s="98"/>
-    </row>
-    <row r="35" spans="1:2">
+      <c r="B34" s="99"/>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A35" s="18" t="s">
         <v>390</v>
       </c>
-      <c r="B35" s="96" t="s">
+      <c r="B35" s="97" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A36" s="17" t="s">
         <v>392</v>
       </c>
-      <c r="B36" s="98"/>
-    </row>
-    <row r="37" spans="1:2">
+      <c r="B36" s="99"/>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A37" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="B37" s="96" t="s">
+      <c r="B37" s="97" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A38" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="B38" s="97"/>
-    </row>
-    <row r="39" spans="1:2">
+      <c r="B38" s="98"/>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A39" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="B39" s="97"/>
-    </row>
-    <row r="40" spans="1:2">
+      <c r="B39" s="98"/>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A40" s="9" t="s">
         <v>393</v>
       </c>
-      <c r="B40" s="96" t="s">
+      <c r="B40" s="97" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A41" s="10" t="s">
         <v>395</v>
       </c>
-      <c r="B41" s="97"/>
-    </row>
-    <row r="42" spans="1:2">
+      <c r="B41" s="98"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A42" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="B42" s="97"/>
-    </row>
-    <row r="43" spans="1:2">
+      <c r="B42" s="98"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A43" s="10" t="s">
         <v>396</v>
       </c>
-      <c r="B43" s="97"/>
-    </row>
-    <row r="44" spans="1:2">
+      <c r="B43" s="98"/>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A44" s="10" t="s">
         <v>397</v>
       </c>
-      <c r="B44" s="97"/>
-    </row>
-    <row r="45" spans="1:2">
+      <c r="B44" s="98"/>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A45" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="B45" s="97"/>
-    </row>
-    <row r="46" spans="1:2">
+      <c r="B45" s="98"/>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A46" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="B46" s="98"/>
-    </row>
-    <row r="47" spans="1:2">
+      <c r="B46" s="99"/>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A47" s="19" t="s">
         <v>85</v>
       </c>
@@ -8164,53 +8184,53 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A48" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="B48" s="96" t="s">
+      <c r="B48" s="97" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A49" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="B49" s="98"/>
-    </row>
-    <row r="50" spans="1:2">
+      <c r="B49" s="99"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A50" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="B50" s="96" t="s">
+      <c r="B50" s="97" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A51" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="B51" s="97"/>
-    </row>
-    <row r="52" spans="1:2">
+      <c r="B51" s="98"/>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A52" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="B52" s="97"/>
-    </row>
-    <row r="53" spans="1:2">
+      <c r="B52" s="98"/>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A53" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="B53" s="97"/>
-    </row>
-    <row r="54" spans="1:2">
+      <c r="B53" s="98"/>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A54" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B54" s="98"/>
-    </row>
-    <row r="55" spans="1:2">
+      <c r="B54" s="99"/>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A55" s="19" t="s">
         <v>399</v>
       </c>
@@ -8218,314 +8238,314 @@
         <v>400</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A56" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="B56" s="96" t="s">
+      <c r="B56" s="97" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A57" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="B57" s="97"/>
-    </row>
-    <row r="58" spans="1:2">
+      <c r="B57" s="98"/>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A58" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="B58" s="98"/>
-    </row>
-    <row r="59" spans="1:2">
+      <c r="B58" s="99"/>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A59" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="B59" s="96" t="s">
+      <c r="B59" s="97" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A60" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="B60" s="97"/>
-    </row>
-    <row r="61" spans="1:2">
+      <c r="B60" s="98"/>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A61" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="B61" s="97"/>
-    </row>
-    <row r="62" spans="1:2">
+      <c r="B61" s="98"/>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A62" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="B62" s="97"/>
-    </row>
-    <row r="63" spans="1:2">
+      <c r="B62" s="98"/>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A63" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="B63" s="97"/>
-    </row>
-    <row r="64" spans="1:2">
+      <c r="B63" s="98"/>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A64" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="B64" s="98"/>
-    </row>
-    <row r="65" spans="1:5" ht="13.5" customHeight="1">
+      <c r="B64" s="99"/>
+    </row>
+    <row r="65" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="10" t="s">
         <v>401</v>
       </c>
-      <c r="B65" s="104" t="s">
+      <c r="B65" s="100" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A66" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B66" s="105"/>
+      <c r="B66" s="101"/>
       <c r="E66" s="22"/>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A67" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="B67" s="105"/>
-    </row>
-    <row r="68" spans="1:5">
+      <c r="B67" s="101"/>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A68" s="10" t="s">
         <v>403</v>
       </c>
-      <c r="B68" s="106"/>
-    </row>
-    <row r="69" spans="1:5">
+      <c r="B68" s="102"/>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A69" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="B69" s="96" t="s">
+      <c r="B69" s="97" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A70" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="B70" s="97"/>
-    </row>
-    <row r="71" spans="1:5">
+      <c r="B70" s="98"/>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A71" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="B71" s="97"/>
-    </row>
-    <row r="72" spans="1:5">
+      <c r="B71" s="98"/>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A72" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="B72" s="97"/>
-    </row>
-    <row r="73" spans="1:5">
+      <c r="B72" s="98"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A73" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="B73" s="97"/>
-    </row>
-    <row r="74" spans="1:5">
+      <c r="B73" s="98"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A74" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="B74" s="98"/>
-    </row>
-    <row r="75" spans="1:5">
+      <c r="B74" s="99"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A75" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="B75" s="96" t="s">
+      <c r="B75" s="97" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A76" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="B76" s="97"/>
-    </row>
-    <row r="77" spans="1:5">
+      <c r="B76" s="98"/>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A77" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="B77" s="97"/>
-    </row>
-    <row r="78" spans="1:5">
+      <c r="B77" s="98"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A78" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="B78" s="97"/>
-    </row>
-    <row r="79" spans="1:5">
+      <c r="B78" s="98"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A79" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="B79" s="97"/>
-    </row>
-    <row r="80" spans="1:5">
+      <c r="B79" s="98"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A80" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="B80" s="97"/>
-    </row>
-    <row r="81" spans="1:2">
+      <c r="B80" s="98"/>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A81" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="B81" s="97"/>
-    </row>
-    <row r="82" spans="1:2">
+      <c r="B81" s="98"/>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A82" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="B82" s="97"/>
-    </row>
-    <row r="83" spans="1:2">
+      <c r="B82" s="98"/>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A83" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="B83" s="97"/>
-    </row>
-    <row r="84" spans="1:2">
+      <c r="B83" s="98"/>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A84" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="B84" s="97"/>
-    </row>
-    <row r="85" spans="1:2">
+      <c r="B84" s="98"/>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A85" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="B85" s="97"/>
-    </row>
-    <row r="86" spans="1:2">
+      <c r="B85" s="98"/>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A86" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="B86" s="97"/>
-    </row>
-    <row r="87" spans="1:2">
+      <c r="B86" s="98"/>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A87" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="B87" s="97"/>
-    </row>
-    <row r="88" spans="1:2">
+      <c r="B87" s="98"/>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A88" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="B88" s="97"/>
-    </row>
-    <row r="89" spans="1:2">
+      <c r="B88" s="98"/>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A89" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="B89" s="97"/>
-    </row>
-    <row r="90" spans="1:2">
+      <c r="B89" s="98"/>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A90" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="B90" s="97"/>
-    </row>
-    <row r="91" spans="1:2">
+      <c r="B90" s="98"/>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A91" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="B91" s="97"/>
-    </row>
-    <row r="92" spans="1:2">
+      <c r="B91" s="98"/>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A92" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="B92" s="97"/>
-    </row>
-    <row r="93" spans="1:2">
+      <c r="B92" s="98"/>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A93" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="B93" s="97"/>
-    </row>
-    <row r="94" spans="1:2">
+      <c r="B93" s="98"/>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A94" s="25" t="s">
         <v>127</v>
       </c>
-      <c r="B94" s="97"/>
-    </row>
-    <row r="95" spans="1:2">
+      <c r="B94" s="98"/>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A95" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="B95" s="97"/>
-    </row>
-    <row r="96" spans="1:2">
+      <c r="B95" s="98"/>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A96" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="B96" s="97"/>
-    </row>
-    <row r="97" spans="1:2">
+      <c r="B96" s="98"/>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A97" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="B97" s="97"/>
-    </row>
-    <row r="98" spans="1:2">
+      <c r="B97" s="98"/>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A98" s="26" t="s">
         <v>139</v>
       </c>
-      <c r="B98" s="101" t="s">
+      <c r="B98" s="94" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="99" spans="1:2" s="5" customFormat="1">
+    <row r="99" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A99" s="25" t="s">
         <v>140</v>
       </c>
-      <c r="B99" s="102"/>
-    </row>
-    <row r="100" spans="1:2" s="5" customFormat="1">
+      <c r="B99" s="95"/>
+    </row>
+    <row r="100" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A100" s="25" t="s">
         <v>141</v>
       </c>
-      <c r="B100" s="102"/>
-    </row>
-    <row r="101" spans="1:2" s="5" customFormat="1">
+      <c r="B100" s="95"/>
+    </row>
+    <row r="101" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A101" s="25" t="s">
         <v>142</v>
       </c>
-      <c r="B101" s="102"/>
-    </row>
-    <row r="102" spans="1:2" s="5" customFormat="1">
+      <c r="B101" s="95"/>
+    </row>
+    <row r="102" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A102" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="B102" s="102"/>
-    </row>
-    <row r="103" spans="1:2" s="5" customFormat="1">
+      <c r="B102" s="95"/>
+    </row>
+    <row r="103" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A103" s="25" t="s">
         <v>144</v>
       </c>
-      <c r="B103" s="102"/>
-    </row>
-    <row r="104" spans="1:2" s="5" customFormat="1">
+      <c r="B103" s="95"/>
+    </row>
+    <row r="104" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A104" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="B104" s="103"/>
-    </row>
-    <row r="105" spans="1:2" s="5" customFormat="1">
+      <c r="B104" s="96"/>
+    </row>
+    <row r="105" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A105" s="27" t="s">
         <v>404</v>
       </c>
@@ -8535,46 +8555,46 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="B11:B24"/>
+    <mergeCell ref="B25:B34"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="B40:B46"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="B50:B54"/>
     <mergeCell ref="B98:B104"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="B59:B64"/>
     <mergeCell ref="B65:B68"/>
     <mergeCell ref="B69:B74"/>
     <mergeCell ref="B75:B97"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="B40:B46"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="B50:B54"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B11:B24"/>
-    <mergeCell ref="B25:B34"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B11:B22" location="资产要素登记!O1" display="债券类资产/理财直接融资工具/同业存单"/>
-    <hyperlink ref="B7:B10" location="资产要素登记!Z1" display="拆放同业/买入返售（资产）||同业拆入/卖出回购（负债）"/>
-    <hyperlink ref="B25:B34" location="资产要素登记!AH1" display="非标准化债权类资产/新增可投资资产"/>
-    <hyperlink ref="B35:B36" location="资产要素登记!CV1" display="票据类资产/信用证类资产"/>
-    <hyperlink ref="B37:B39" location="资产要素登记!DH1" display="权益类资产"/>
-    <hyperlink ref="B40:B46" location="资产要素登记!DS1" display="金融衍生品"/>
-    <hyperlink ref="B47" location="资产要素登记!DW1" display="QDII债券资产"/>
-    <hyperlink ref="B48:B49" location="资产要素登记!EK1" display="QDII拆出/逆回购资产"/>
-    <hyperlink ref="B50:B54" location="资产要素登记!EQ1" display="QDII股票/基金类资产"/>
-    <hyperlink ref="B55" location="资产要素登记!EV1" display="QDII结构性票据类资产"/>
-    <hyperlink ref="B56:B58" location="资产要素登记!GJ1" display="贵金属/商品"/>
-    <hyperlink ref="B59:B63" location="资产要素登记!EF1" display="资产管理产品"/>
-    <hyperlink ref="B69:B74" location="资产要素登记!HS1" display="另类资产"/>
-    <hyperlink ref="B75:B97" location="资产要素登记!HY1" display="公募基金/私募基金"/>
-    <hyperlink ref="B105" location="资产要素登记!JH1" display="其他（负债）类资产"/>
-    <hyperlink ref="B3:B5" location="资产要素登记!E1" display="本行/他行存款||大额存单"/>
-    <hyperlink ref="B3:B6" location="资产要素登记!F1" display="本行/他行存款||大额存单"/>
-    <hyperlink ref="B98:B104" location="资产要素登记!IN1" display="委外投资——协议方式"/>
-    <hyperlink ref="B65" location="资产要素登记!FH1" display="其他非标准化债权类投资、其他权益类投资、其他代客境外理财投资QDII、其他新增可投资资产"/>
-    <hyperlink ref="B59:B64" location="资产要素登记!FM1" display="资产管理产品"/>
-    <hyperlink ref="B65:B68" location="资产要素登记!GO1" display="其他非标准化债权类投资、其他权益类投资、其他代客境外理财投资QDII、其他新增可投资资产"/>
+    <hyperlink ref="B11:B22" location="资产要素登记!O1" display="债券类资产/理财直接融资工具/同业存单" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
+    <hyperlink ref="B7:B10" location="资产要素登记!Z1" display="拆放同业/买入返售（资产）||同业拆入/卖出回购（负债）" xr:uid="{00000000-0004-0000-0300-000001000000}"/>
+    <hyperlink ref="B25:B34" location="资产要素登记!AH1" display="非标准化债权类资产/新增可投资资产" xr:uid="{00000000-0004-0000-0300-000002000000}"/>
+    <hyperlink ref="B35:B36" location="资产要素登记!CV1" display="票据类资产/信用证类资产" xr:uid="{00000000-0004-0000-0300-000003000000}"/>
+    <hyperlink ref="B37:B39" location="资产要素登记!DH1" display="权益类资产" xr:uid="{00000000-0004-0000-0300-000004000000}"/>
+    <hyperlink ref="B40:B46" location="资产要素登记!DS1" display="金融衍生品" xr:uid="{00000000-0004-0000-0300-000005000000}"/>
+    <hyperlink ref="B47" location="资产要素登记!DW1" display="QDII债券资产" xr:uid="{00000000-0004-0000-0300-000006000000}"/>
+    <hyperlink ref="B48:B49" location="资产要素登记!EK1" display="QDII拆出/逆回购资产" xr:uid="{00000000-0004-0000-0300-000007000000}"/>
+    <hyperlink ref="B50:B54" location="资产要素登记!EQ1" display="QDII股票/基金类资产" xr:uid="{00000000-0004-0000-0300-000008000000}"/>
+    <hyperlink ref="B55" location="资产要素登记!EV1" display="QDII结构性票据类资产" xr:uid="{00000000-0004-0000-0300-000009000000}"/>
+    <hyperlink ref="B56:B58" location="资产要素登记!GJ1" display="贵金属/商品" xr:uid="{00000000-0004-0000-0300-00000A000000}"/>
+    <hyperlink ref="B59:B63" location="资产要素登记!EF1" display="资产管理产品" xr:uid="{00000000-0004-0000-0300-00000B000000}"/>
+    <hyperlink ref="B69:B74" location="资产要素登记!HS1" display="另类资产" xr:uid="{00000000-0004-0000-0300-00000C000000}"/>
+    <hyperlink ref="B75:B97" location="资产要素登记!HY1" display="公募基金/私募基金" xr:uid="{00000000-0004-0000-0300-00000D000000}"/>
+    <hyperlink ref="B105" location="资产要素登记!JH1" display="其他（负债）类资产" xr:uid="{00000000-0004-0000-0300-00000E000000}"/>
+    <hyperlink ref="B3:B5" location="资产要素登记!E1" display="本行/他行存款||大额存单" xr:uid="{00000000-0004-0000-0300-00000F000000}"/>
+    <hyperlink ref="B3:B6" location="资产要素登记!F1" display="本行/他行存款||大额存单" xr:uid="{00000000-0004-0000-0300-000010000000}"/>
+    <hyperlink ref="B98:B104" location="资产要素登记!IN1" display="委外投资——协议方式" xr:uid="{00000000-0004-0000-0300-000011000000}"/>
+    <hyperlink ref="B65" location="资产要素登记!FH1" display="其他非标准化债权类投资、其他权益类投资、其他代客境外理财投资QDII、其他新增可投资资产" xr:uid="{00000000-0004-0000-0300-000012000000}"/>
+    <hyperlink ref="B59:B64" location="资产要素登记!FM1" display="资产管理产品" xr:uid="{00000000-0004-0000-0300-000013000000}"/>
+    <hyperlink ref="B65:B68" location="资产要素登记!GO1" display="其他非标准化债权类投资、其他权益类投资、其他代客境外理财投资QDII、其他新增可投资资产" xr:uid="{00000000-0004-0000-0300-000014000000}"/>
   </hyperlinks>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -8582,1208 +8602,1208 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:IS239"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="35.5" style="2" customWidth="1"/>
     <col min="2" max="253" width="9.125" style="2"/>
     <col min="254" max="16384" width="9.125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="27" customHeight="1">
+    <row r="1" spans="1:1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A2" s="2" t="s">
         <v>693</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="2" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A3" s="2" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="2" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A4" s="2" t="s">
         <v>695</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="2" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A5" s="2" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="2" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A6" s="2" t="s">
         <v>697</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="2" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A7" s="2" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="2" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A8" s="2" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="2" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A9" s="2" t="s">
         <v>700</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="2" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A10" s="2" t="s">
         <v>701</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="2" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A11" s="3" t="s">
         <v>702</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="3" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A12" s="2" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="2" t="s">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A13" s="2" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="2" t="s">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A14" s="2" t="s">
         <v>705</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="2" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A15" s="2" t="s">
         <v>706</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="2" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A16" s="2" t="s">
         <v>707</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="2" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A17" s="2" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="2" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A18" s="2" t="s">
         <v>709</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="2" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A19" s="2" t="s">
         <v>710</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="2" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A20" s="2" t="s">
         <v>711</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="2" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A21" s="2" t="s">
         <v>712</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="2" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A22" s="2" t="s">
         <v>713</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="2" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A23" s="2" t="s">
         <v>714</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="2" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A24" s="2" t="s">
         <v>715</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="2" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A25" s="2" t="s">
         <v>716</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="2" t="s">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A26" s="2" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
-      <c r="A26" s="2" t="s">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A27" s="2" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="2" t="s">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A28" s="2" t="s">
         <v>719</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="2" t="s">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A29" s="2" t="s">
         <v>720</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="2" t="s">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A30" s="2" t="s">
         <v>721</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="2" t="s">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A31" s="2" t="s">
         <v>722</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="2" t="s">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A32" s="2" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="2" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A33" s="2" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="2" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A34" s="2" t="s">
         <v>725</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="2" t="s">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A35" s="2" t="s">
         <v>726</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="2" t="s">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A36" s="2" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="2" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A37" s="2" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="2" t="s">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A38" s="2" t="s">
         <v>729</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="2" t="s">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A39" s="2" t="s">
         <v>730</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="2" t="s">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A40" s="2" t="s">
         <v>731</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="2" t="s">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A41" s="2" t="s">
         <v>732</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="2" t="s">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A42" s="2" t="s">
         <v>733</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="2" t="s">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A43" s="2" t="s">
         <v>734</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="2" t="s">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A44" s="2" t="s">
         <v>735</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
-      <c r="A44" s="2" t="s">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A45" s="2" t="s">
         <v>736</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="2" t="s">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A46" s="2" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
-      <c r="A46" s="2" t="s">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A47" s="2" t="s">
         <v>738</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
-      <c r="A47" s="2" t="s">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A48" s="2" t="s">
         <v>739</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="2" t="s">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A49" s="2" t="s">
         <v>740</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
-      <c r="A49" s="2" t="s">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A50" s="2" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
-      <c r="A50" s="2" t="s">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A51" s="2" t="s">
         <v>742</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
-      <c r="A51" s="2" t="s">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A52" s="2" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
-      <c r="A52" s="2" t="s">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A53" s="2" t="s">
         <v>744</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
-      <c r="A53" s="2" t="s">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A54" s="2" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
-      <c r="A54" s="2" t="s">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A55" s="2" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
-      <c r="A55" s="2" t="s">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A56" s="2" t="s">
         <v>747</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
-      <c r="A56" s="2" t="s">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A57" s="2" t="s">
         <v>748</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
-      <c r="A57" s="2" t="s">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A58" s="2" t="s">
         <v>749</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
-      <c r="A58" s="2" t="s">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A59" s="2" t="s">
         <v>750</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
-      <c r="A59" s="2" t="s">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A60" s="2" t="s">
         <v>751</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
-      <c r="A60" s="2" t="s">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A61" s="2" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
-      <c r="A61" s="2" t="s">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A62" s="2" t="s">
         <v>753</v>
       </c>
     </row>
-    <row r="62" spans="1:1">
-      <c r="A62" s="2" t="s">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A63" s="2" t="s">
         <v>754</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
-      <c r="A63" s="2" t="s">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A64" s="2" t="s">
         <v>755</v>
       </c>
     </row>
-    <row r="64" spans="1:1">
-      <c r="A64" s="2" t="s">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A65" s="2" t="s">
         <v>756</v>
       </c>
     </row>
-    <row r="65" spans="1:1">
-      <c r="A65" s="2" t="s">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A66" s="2" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="66" spans="1:1">
-      <c r="A66" s="2" t="s">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A67" s="2" t="s">
         <v>758</v>
       </c>
     </row>
-    <row r="67" spans="1:1">
-      <c r="A67" s="2" t="s">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A68" s="2" t="s">
         <v>759</v>
       </c>
     </row>
-    <row r="68" spans="1:1">
-      <c r="A68" s="2" t="s">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A69" s="2" t="s">
         <v>760</v>
       </c>
     </row>
-    <row r="69" spans="1:1">
-      <c r="A69" s="2" t="s">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A70" s="2" t="s">
         <v>761</v>
       </c>
     </row>
-    <row r="70" spans="1:1">
-      <c r="A70" s="2" t="s">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A71" s="2" t="s">
         <v>762</v>
       </c>
     </row>
-    <row r="71" spans="1:1">
-      <c r="A71" s="2" t="s">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A72" s="2" t="s">
         <v>763</v>
       </c>
     </row>
-    <row r="72" spans="1:1">
-      <c r="A72" s="2" t="s">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A73" s="2" t="s">
         <v>764</v>
       </c>
     </row>
-    <row r="73" spans="1:1">
-      <c r="A73" s="2" t="s">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A74" s="2" t="s">
         <v>765</v>
       </c>
     </row>
-    <row r="74" spans="1:1">
-      <c r="A74" s="2" t="s">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A75" s="2" t="s">
         <v>766</v>
       </c>
     </row>
-    <row r="75" spans="1:1">
-      <c r="A75" s="2" t="s">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A76" s="2" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="76" spans="1:1">
-      <c r="A76" s="2" t="s">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A77" s="2" t="s">
         <v>768</v>
       </c>
     </row>
-    <row r="77" spans="1:1">
-      <c r="A77" s="2" t="s">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A78" s="2" t="s">
         <v>769</v>
       </c>
     </row>
-    <row r="78" spans="1:1">
-      <c r="A78" s="2" t="s">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A79" s="2" t="s">
         <v>770</v>
       </c>
     </row>
-    <row r="79" spans="1:1">
-      <c r="A79" s="2" t="s">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A80" s="2" t="s">
         <v>771</v>
       </c>
     </row>
-    <row r="80" spans="1:1">
-      <c r="A80" s="2" t="s">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A81" s="2" t="s">
         <v>772</v>
       </c>
     </row>
-    <row r="81" spans="1:1">
-      <c r="A81" s="2" t="s">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A82" s="2" t="s">
         <v>773</v>
       </c>
     </row>
-    <row r="82" spans="1:1">
-      <c r="A82" s="2" t="s">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A83" s="2" t="s">
         <v>774</v>
       </c>
     </row>
-    <row r="83" spans="1:1">
-      <c r="A83" s="2" t="s">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A84" s="2" t="s">
         <v>775</v>
       </c>
     </row>
-    <row r="84" spans="1:1">
-      <c r="A84" s="2" t="s">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A85" s="2" t="s">
         <v>776</v>
       </c>
     </row>
-    <row r="85" spans="1:1">
-      <c r="A85" s="2" t="s">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A86" s="2" t="s">
         <v>777</v>
       </c>
     </row>
-    <row r="86" spans="1:1">
-      <c r="A86" s="2" t="s">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A87" s="2" t="s">
         <v>778</v>
       </c>
     </row>
-    <row r="87" spans="1:1">
-      <c r="A87" s="2" t="s">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A88" s="2" t="s">
         <v>779</v>
       </c>
     </row>
-    <row r="88" spans="1:1">
-      <c r="A88" s="2" t="s">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A89" s="2" t="s">
         <v>780</v>
       </c>
     </row>
-    <row r="89" spans="1:1">
-      <c r="A89" s="2" t="s">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A90" s="2" t="s">
         <v>781</v>
       </c>
     </row>
-    <row r="90" spans="1:1">
-      <c r="A90" s="2" t="s">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A91" s="2" t="s">
         <v>782</v>
       </c>
     </row>
-    <row r="91" spans="1:1">
-      <c r="A91" s="2" t="s">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A92" s="2" t="s">
         <v>783</v>
       </c>
     </row>
-    <row r="92" spans="1:1">
-      <c r="A92" s="2" t="s">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A93" s="2" t="s">
         <v>784</v>
       </c>
     </row>
-    <row r="93" spans="1:1">
-      <c r="A93" s="2" t="s">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A94" s="2" t="s">
         <v>785</v>
       </c>
     </row>
-    <row r="94" spans="1:1">
-      <c r="A94" s="2" t="s">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A95" s="2" t="s">
         <v>786</v>
       </c>
     </row>
-    <row r="95" spans="1:1">
-      <c r="A95" s="2" t="s">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A96" s="2" t="s">
         <v>787</v>
       </c>
     </row>
-    <row r="96" spans="1:1">
-      <c r="A96" s="2" t="s">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A97" s="2" t="s">
         <v>788</v>
       </c>
     </row>
-    <row r="97" spans="1:1">
-      <c r="A97" s="2" t="s">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A98" s="2" t="s">
         <v>789</v>
       </c>
     </row>
-    <row r="98" spans="1:1">
-      <c r="A98" s="2" t="s">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A99" s="2" t="s">
         <v>790</v>
       </c>
     </row>
-    <row r="99" spans="1:1">
-      <c r="A99" s="2" t="s">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A100" s="2" t="s">
         <v>791</v>
       </c>
     </row>
-    <row r="100" spans="1:1">
-      <c r="A100" s="2" t="s">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A101" s="2" t="s">
         <v>792</v>
       </c>
     </row>
-    <row r="101" spans="1:1">
-      <c r="A101" s="2" t="s">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A102" s="2" t="s">
         <v>793</v>
       </c>
     </row>
-    <row r="102" spans="1:1">
-      <c r="A102" s="2" t="s">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A103" s="2" t="s">
         <v>794</v>
       </c>
     </row>
-    <row r="103" spans="1:1">
-      <c r="A103" s="2" t="s">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A104" s="2" t="s">
         <v>795</v>
       </c>
     </row>
-    <row r="104" spans="1:1">
-      <c r="A104" s="2" t="s">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A105" s="2" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="105" spans="1:1">
-      <c r="A105" s="2" t="s">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A106" s="2" t="s">
         <v>797</v>
       </c>
     </row>
-    <row r="106" spans="1:1">
-      <c r="A106" s="2" t="s">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A107" s="2" t="s">
         <v>798</v>
       </c>
     </row>
-    <row r="107" spans="1:1">
-      <c r="A107" s="2" t="s">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A108" s="2" t="s">
         <v>799</v>
       </c>
     </row>
-    <row r="108" spans="1:1">
-      <c r="A108" s="2" t="s">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A109" s="2" t="s">
         <v>800</v>
       </c>
     </row>
-    <row r="109" spans="1:1">
-      <c r="A109" s="2" t="s">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A110" s="2" t="s">
         <v>801</v>
       </c>
     </row>
-    <row r="110" spans="1:1">
-      <c r="A110" s="2" t="s">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A111" s="2" t="s">
         <v>802</v>
       </c>
     </row>
-    <row r="111" spans="1:1">
-      <c r="A111" s="2" t="s">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A112" s="2" t="s">
         <v>803</v>
       </c>
     </row>
-    <row r="112" spans="1:1">
-      <c r="A112" s="2" t="s">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A113" s="2" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="113" spans="1:1">
-      <c r="A113" s="2" t="s">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A114" s="2" t="s">
         <v>805</v>
       </c>
     </row>
-    <row r="114" spans="1:1">
-      <c r="A114" s="2" t="s">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A115" s="2" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="115" spans="1:1">
-      <c r="A115" s="2" t="s">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A116" s="2" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="116" spans="1:1">
-      <c r="A116" s="2" t="s">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A117" s="2" t="s">
         <v>808</v>
       </c>
     </row>
-    <row r="117" spans="1:1">
-      <c r="A117" s="2" t="s">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A118" s="2" t="s">
         <v>809</v>
       </c>
     </row>
-    <row r="118" spans="1:1">
-      <c r="A118" s="2" t="s">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A119" s="2" t="s">
         <v>810</v>
       </c>
     </row>
-    <row r="119" spans="1:1">
-      <c r="A119" s="2" t="s">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A120" s="2" t="s">
         <v>811</v>
       </c>
     </row>
-    <row r="120" spans="1:1">
-      <c r="A120" s="2" t="s">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A121" s="2" t="s">
         <v>812</v>
       </c>
     </row>
-    <row r="121" spans="1:1">
-      <c r="A121" s="2" t="s">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A122" s="2" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="122" spans="1:1">
-      <c r="A122" s="2" t="s">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A123" s="2" t="s">
         <v>814</v>
       </c>
     </row>
-    <row r="123" spans="1:1">
-      <c r="A123" s="2" t="s">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A124" s="2" t="s">
         <v>815</v>
       </c>
     </row>
-    <row r="124" spans="1:1">
-      <c r="A124" s="2" t="s">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A125" s="2" t="s">
         <v>816</v>
       </c>
     </row>
-    <row r="125" spans="1:1">
-      <c r="A125" s="2" t="s">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A126" s="2" t="s">
         <v>817</v>
       </c>
     </row>
-    <row r="126" spans="1:1">
-      <c r="A126" s="2" t="s">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A127" s="2" t="s">
         <v>818</v>
       </c>
     </row>
-    <row r="127" spans="1:1">
-      <c r="A127" s="2" t="s">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A128" s="2" t="s">
         <v>819</v>
       </c>
     </row>
-    <row r="128" spans="1:1">
-      <c r="A128" s="2" t="s">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A129" s="2" t="s">
         <v>820</v>
       </c>
     </row>
-    <row r="129" spans="1:1">
-      <c r="A129" s="2" t="s">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A130" s="2" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="130" spans="1:1">
-      <c r="A130" s="2" t="s">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A131" s="2" t="s">
         <v>822</v>
       </c>
     </row>
-    <row r="131" spans="1:1">
-      <c r="A131" s="2" t="s">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A132" s="2" t="s">
         <v>823</v>
       </c>
     </row>
-    <row r="132" spans="1:1">
-      <c r="A132" s="2" t="s">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A133" s="2" t="s">
         <v>824</v>
       </c>
     </row>
-    <row r="133" spans="1:1">
-      <c r="A133" s="2" t="s">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A134" s="2" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="134" spans="1:1">
-      <c r="A134" s="2" t="s">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A135" s="2" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="135" spans="1:1">
-      <c r="A135" s="2" t="s">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A136" s="2" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="136" spans="1:1">
-      <c r="A136" s="2" t="s">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A137" s="2" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="137" spans="1:1">
-      <c r="A137" s="2" t="s">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A138" s="2" t="s">
         <v>829</v>
       </c>
     </row>
-    <row r="138" spans="1:1">
-      <c r="A138" s="2" t="s">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A139" s="2" t="s">
         <v>830</v>
       </c>
     </row>
-    <row r="139" spans="1:1">
-      <c r="A139" s="2" t="s">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A140" s="2" t="s">
         <v>831</v>
       </c>
     </row>
-    <row r="140" spans="1:1">
-      <c r="A140" s="2" t="s">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A141" s="2" t="s">
         <v>832</v>
       </c>
     </row>
-    <row r="141" spans="1:1">
-      <c r="A141" s="2" t="s">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A142" s="2" t="s">
         <v>833</v>
       </c>
     </row>
-    <row r="142" spans="1:1">
-      <c r="A142" s="2" t="s">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A143" s="2" t="s">
         <v>834</v>
       </c>
     </row>
-    <row r="143" spans="1:1">
-      <c r="A143" s="2" t="s">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A144" s="2" t="s">
         <v>835</v>
       </c>
     </row>
-    <row r="144" spans="1:1">
-      <c r="A144" s="2" t="s">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A145" s="2" t="s">
         <v>836</v>
       </c>
     </row>
-    <row r="145" spans="1:1">
-      <c r="A145" s="2" t="s">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A146" s="2" t="s">
         <v>837</v>
       </c>
     </row>
-    <row r="146" spans="1:1">
-      <c r="A146" s="2" t="s">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A147" s="2" t="s">
         <v>838</v>
       </c>
     </row>
-    <row r="147" spans="1:1">
-      <c r="A147" s="2" t="s">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A148" s="2" t="s">
         <v>839</v>
       </c>
     </row>
-    <row r="148" spans="1:1">
-      <c r="A148" s="2" t="s">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A149" s="2" t="s">
         <v>840</v>
       </c>
     </row>
-    <row r="149" spans="1:1">
-      <c r="A149" s="2" t="s">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A150" s="2" t="s">
         <v>841</v>
       </c>
     </row>
-    <row r="150" spans="1:1">
-      <c r="A150" s="2" t="s">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A151" s="2" t="s">
         <v>842</v>
       </c>
     </row>
-    <row r="151" spans="1:1">
-      <c r="A151" s="2" t="s">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A152" s="2" t="s">
         <v>843</v>
       </c>
     </row>
-    <row r="152" spans="1:1">
-      <c r="A152" s="2" t="s">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A153" s="2" t="s">
         <v>844</v>
       </c>
     </row>
-    <row r="153" spans="1:1">
-      <c r="A153" s="2" t="s">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A154" s="2" t="s">
         <v>845</v>
       </c>
     </row>
-    <row r="154" spans="1:1">
-      <c r="A154" s="2" t="s">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A155" s="2" t="s">
         <v>846</v>
       </c>
     </row>
-    <row r="155" spans="1:1">
-      <c r="A155" s="2" t="s">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A156" s="2" t="s">
         <v>847</v>
       </c>
     </row>
-    <row r="156" spans="1:1">
-      <c r="A156" s="2" t="s">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A157" s="2" t="s">
         <v>848</v>
       </c>
     </row>
-    <row r="157" spans="1:1">
-      <c r="A157" s="2" t="s">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A158" s="2" t="s">
         <v>849</v>
       </c>
     </row>
-    <row r="158" spans="1:1">
-      <c r="A158" s="2" t="s">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A159" s="2" t="s">
         <v>850</v>
       </c>
     </row>
-    <row r="159" spans="1:1">
-      <c r="A159" s="2" t="s">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A160" s="2" t="s">
         <v>851</v>
       </c>
     </row>
-    <row r="160" spans="1:1">
-      <c r="A160" s="2" t="s">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A161" s="2" t="s">
         <v>852</v>
       </c>
     </row>
-    <row r="161" spans="1:1">
-      <c r="A161" s="2" t="s">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A162" s="2" t="s">
         <v>853</v>
       </c>
     </row>
-    <row r="162" spans="1:1">
-      <c r="A162" s="2" t="s">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A163" s="2" t="s">
         <v>854</v>
       </c>
     </row>
-    <row r="163" spans="1:1">
-      <c r="A163" s="2" t="s">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A164" s="2" t="s">
         <v>855</v>
       </c>
     </row>
-    <row r="164" spans="1:1">
-      <c r="A164" s="2" t="s">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A165" s="2" t="s">
         <v>856</v>
       </c>
     </row>
-    <row r="165" spans="1:1">
-      <c r="A165" s="2" t="s">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A166" s="2" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="166" spans="1:1">
-      <c r="A166" s="2" t="s">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A167" s="2" t="s">
         <v>858</v>
       </c>
     </row>
-    <row r="167" spans="1:1">
-      <c r="A167" s="2" t="s">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A168" s="2" t="s">
         <v>859</v>
       </c>
     </row>
-    <row r="168" spans="1:1">
-      <c r="A168" s="2" t="s">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A169" s="2" t="s">
         <v>860</v>
       </c>
     </row>
-    <row r="169" spans="1:1">
-      <c r="A169" s="2" t="s">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A170" s="2" t="s">
         <v>861</v>
       </c>
     </row>
-    <row r="170" spans="1:1">
-      <c r="A170" s="2" t="s">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A171" s="2" t="s">
         <v>862</v>
       </c>
     </row>
-    <row r="171" spans="1:1">
-      <c r="A171" s="2" t="s">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A172" s="2" t="s">
         <v>863</v>
       </c>
     </row>
-    <row r="172" spans="1:1">
-      <c r="A172" s="2" t="s">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A173" s="2" t="s">
         <v>864</v>
       </c>
     </row>
-    <row r="173" spans="1:1">
-      <c r="A173" s="2" t="s">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A174" s="2" t="s">
         <v>865</v>
       </c>
     </row>
-    <row r="174" spans="1:1">
-      <c r="A174" s="2" t="s">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A175" s="2" t="s">
         <v>866</v>
       </c>
     </row>
-    <row r="175" spans="1:1">
-      <c r="A175" s="2" t="s">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A176" s="2" t="s">
         <v>867</v>
       </c>
     </row>
-    <row r="176" spans="1:1">
-      <c r="A176" s="2" t="s">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A177" s="2" t="s">
         <v>868</v>
       </c>
     </row>
-    <row r="177" spans="1:1">
-      <c r="A177" s="2" t="s">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A178" s="2" t="s">
         <v>869</v>
       </c>
     </row>
-    <row r="178" spans="1:1">
-      <c r="A178" s="2" t="s">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A179" s="2" t="s">
         <v>870</v>
       </c>
     </row>
-    <row r="179" spans="1:1">
-      <c r="A179" s="2" t="s">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A180" s="2" t="s">
         <v>871</v>
       </c>
     </row>
-    <row r="180" spans="1:1">
-      <c r="A180" s="2" t="s">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A181" s="2" t="s">
         <v>872</v>
       </c>
     </row>
-    <row r="181" spans="1:1">
-      <c r="A181" s="2" t="s">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A182" s="2" t="s">
         <v>873</v>
       </c>
     </row>
-    <row r="182" spans="1:1">
-      <c r="A182" s="2" t="s">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A183" s="2" t="s">
         <v>874</v>
       </c>
     </row>
-    <row r="183" spans="1:1">
-      <c r="A183" s="2" t="s">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A184" s="2" t="s">
         <v>875</v>
       </c>
     </row>
-    <row r="184" spans="1:1">
-      <c r="A184" s="2" t="s">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A185" s="2" t="s">
         <v>876</v>
       </c>
     </row>
-    <row r="185" spans="1:1">
-      <c r="A185" s="2" t="s">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A186" s="2" t="s">
         <v>877</v>
       </c>
     </row>
-    <row r="186" spans="1:1">
-      <c r="A186" s="2" t="s">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A187" s="2" t="s">
         <v>878</v>
       </c>
     </row>
-    <row r="187" spans="1:1">
-      <c r="A187" s="2" t="s">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A188" s="2" t="s">
         <v>879</v>
       </c>
     </row>
-    <row r="188" spans="1:1">
-      <c r="A188" s="2" t="s">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A189" s="2" t="s">
         <v>880</v>
       </c>
     </row>
-    <row r="189" spans="1:1">
-      <c r="A189" s="2" t="s">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A190" s="2" t="s">
         <v>881</v>
       </c>
     </row>
-    <row r="190" spans="1:1">
-      <c r="A190" s="2" t="s">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A191" s="2" t="s">
         <v>882</v>
       </c>
     </row>
-    <row r="191" spans="1:1">
-      <c r="A191" s="2" t="s">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A192" s="2" t="s">
         <v>883</v>
       </c>
     </row>
-    <row r="192" spans="1:1">
-      <c r="A192" s="2" t="s">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A193" s="2" t="s">
         <v>884</v>
       </c>
     </row>
-    <row r="193" spans="1:1">
-      <c r="A193" s="2" t="s">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A194" s="2" t="s">
         <v>885</v>
       </c>
     </row>
-    <row r="194" spans="1:1">
-      <c r="A194" s="2" t="s">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A195" s="2" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="195" spans="1:1">
-      <c r="A195" s="2" t="s">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A196" s="2" t="s">
         <v>887</v>
       </c>
     </row>
-    <row r="196" spans="1:1">
-      <c r="A196" s="2" t="s">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A197" s="2" t="s">
         <v>888</v>
       </c>
     </row>
-    <row r="197" spans="1:1">
-      <c r="A197" s="2" t="s">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A198" s="2" t="s">
         <v>889</v>
       </c>
     </row>
-    <row r="198" spans="1:1">
-      <c r="A198" s="2" t="s">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A199" s="2" t="s">
         <v>890</v>
       </c>
     </row>
-    <row r="199" spans="1:1">
-      <c r="A199" s="2" t="s">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A200" s="2" t="s">
         <v>891</v>
       </c>
     </row>
-    <row r="200" spans="1:1">
-      <c r="A200" s="2" t="s">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A201" s="2" t="s">
         <v>892</v>
       </c>
     </row>
-    <row r="201" spans="1:1">
-      <c r="A201" s="2" t="s">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A202" s="2" t="s">
         <v>893</v>
       </c>
     </row>
-    <row r="202" spans="1:1">
-      <c r="A202" s="2" t="s">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A203" s="2" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="203" spans="1:1">
-      <c r="A203" s="2" t="s">
+    <row r="204" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A204" s="2" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="204" spans="1:1">
-      <c r="A204" s="2" t="s">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A205" s="2" t="s">
         <v>896</v>
       </c>
     </row>
-    <row r="205" spans="1:1">
-      <c r="A205" s="2" t="s">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A206" s="2" t="s">
         <v>897</v>
       </c>
     </row>
-    <row r="206" spans="1:1">
-      <c r="A206" s="2" t="s">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A207" s="2" t="s">
         <v>898</v>
       </c>
     </row>
-    <row r="207" spans="1:1">
-      <c r="A207" s="2" t="s">
+    <row r="208" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A208" s="2" t="s">
         <v>899</v>
       </c>
     </row>
-    <row r="208" spans="1:1">
-      <c r="A208" s="2" t="s">
+    <row r="209" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A209" s="2" t="s">
         <v>900</v>
       </c>
     </row>
-    <row r="209" spans="1:1">
-      <c r="A209" s="2" t="s">
+    <row r="210" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A210" s="2" t="s">
         <v>901</v>
       </c>
     </row>
-    <row r="210" spans="1:1">
-      <c r="A210" s="2" t="s">
+    <row r="211" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A211" s="2" t="s">
         <v>902</v>
       </c>
     </row>
-    <row r="211" spans="1:1">
-      <c r="A211" s="2" t="s">
+    <row r="212" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A212" s="2" t="s">
         <v>903</v>
       </c>
     </row>
-    <row r="212" spans="1:1">
-      <c r="A212" s="2" t="s">
+    <row r="213" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A213" s="2" t="s">
         <v>904</v>
       </c>
     </row>
-    <row r="213" spans="1:1">
-      <c r="A213" s="2" t="s">
+    <row r="214" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A214" s="2" t="s">
         <v>905</v>
       </c>
     </row>
-    <row r="214" spans="1:1">
-      <c r="A214" s="2" t="s">
+    <row r="215" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A215" s="2" t="s">
         <v>906</v>
       </c>
     </row>
-    <row r="215" spans="1:1">
-      <c r="A215" s="2" t="s">
+    <row r="216" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A216" s="2" t="s">
         <v>907</v>
       </c>
     </row>
-    <row r="216" spans="1:1">
-      <c r="A216" s="2" t="s">
+    <row r="217" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A217" s="2" t="s">
         <v>908</v>
       </c>
     </row>
-    <row r="217" spans="1:1">
-      <c r="A217" s="2" t="s">
+    <row r="218" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A218" s="2" t="s">
         <v>909</v>
       </c>
     </row>
-    <row r="218" spans="1:1">
-      <c r="A218" s="2" t="s">
+    <row r="219" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A219" s="2" t="s">
         <v>910</v>
       </c>
     </row>
-    <row r="219" spans="1:1">
-      <c r="A219" s="2" t="s">
+    <row r="220" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A220" s="2" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="220" spans="1:1">
-      <c r="A220" s="2" t="s">
+    <row r="221" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A221" s="2" t="s">
         <v>912</v>
       </c>
     </row>
-    <row r="221" spans="1:1">
-      <c r="A221" s="2" t="s">
+    <row r="222" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A222" s="2" t="s">
         <v>913</v>
       </c>
     </row>
-    <row r="222" spans="1:1">
-      <c r="A222" s="2" t="s">
+    <row r="223" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A223" s="2" t="s">
         <v>914</v>
       </c>
     </row>
-    <row r="223" spans="1:1">
-      <c r="A223" s="2" t="s">
+    <row r="224" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A224" s="2" t="s">
         <v>915</v>
       </c>
     </row>
-    <row r="224" spans="1:1">
-      <c r="A224" s="2" t="s">
+    <row r="225" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A225" s="2" t="s">
         <v>916</v>
       </c>
     </row>
-    <row r="225" spans="1:1">
-      <c r="A225" s="2" t="s">
+    <row r="226" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A226" s="2" t="s">
         <v>917</v>
       </c>
     </row>
-    <row r="226" spans="1:1">
-      <c r="A226" s="2" t="s">
+    <row r="227" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A227" s="2" t="s">
         <v>918</v>
       </c>
     </row>
-    <row r="227" spans="1:1">
-      <c r="A227" s="2" t="s">
+    <row r="228" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A228" s="2" t="s">
         <v>919</v>
       </c>
     </row>
-    <row r="228" spans="1:1">
-      <c r="A228" s="2" t="s">
+    <row r="229" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A229" s="2" t="s">
         <v>920</v>
       </c>
     </row>
-    <row r="229" spans="1:1">
-      <c r="A229" s="2" t="s">
+    <row r="230" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A230" s="2" t="s">
         <v>921</v>
       </c>
     </row>
-    <row r="230" spans="1:1">
-      <c r="A230" s="2" t="s">
+    <row r="231" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A231" s="2" t="s">
         <v>922</v>
       </c>
     </row>
-    <row r="231" spans="1:1">
-      <c r="A231" s="2" t="s">
+    <row r="232" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A232" s="2" t="s">
         <v>923</v>
       </c>
     </row>
-    <row r="232" spans="1:1">
-      <c r="A232" s="2" t="s">
+    <row r="233" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A233" s="2" t="s">
         <v>924</v>
       </c>
     </row>
-    <row r="233" spans="1:1">
-      <c r="A233" s="2" t="s">
+    <row r="234" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A234" s="2" t="s">
         <v>925</v>
       </c>
     </row>
-    <row r="234" spans="1:1">
-      <c r="A234" s="2" t="s">
+    <row r="235" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A235" s="2" t="s">
         <v>926</v>
       </c>
     </row>
-    <row r="235" spans="1:1">
-      <c r="A235" s="2" t="s">
+    <row r="236" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A236" s="2" t="s">
         <v>927</v>
       </c>
     </row>
-    <row r="236" spans="1:1">
-      <c r="A236" s="2" t="s">
+    <row r="237" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A237" s="2" t="s">
         <v>928</v>
       </c>
     </row>
-    <row r="237" spans="1:1">
-      <c r="A237" s="2" t="s">
+    <row r="238" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A238" s="2" t="s">
         <v>929</v>
       </c>
     </row>
-    <row r="238" spans="1:1">
-      <c r="A238" s="2" t="s">
+    <row r="239" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A239" s="2" t="s">
         <v>930</v>
-      </c>
-    </row>
-    <row r="239" spans="1:1">
-      <c r="A239" s="2" t="s">
-        <v>931</v>
       </c>
     </row>
   </sheetData>
@@ -9793,902 +9813,902 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:A178"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="35.625" style="1" customWidth="1"/>
     <col min="2" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A2" s="1" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="1" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A3" s="1" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A4" s="1" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="1" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A5" s="1" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="1" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A6" s="1" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A7" s="1" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="1" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A8" s="1" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="1" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A9" s="1" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A10" s="1" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="1" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A11" s="1" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="1" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A12" s="1" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A13" s="1" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="1" t="s">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A14" s="1" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="1" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A15" s="1" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="1" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A16" s="1" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="1" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A17" s="1" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="1" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A18" s="1" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="1" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A19" s="1" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="1" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A20" s="1" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="1" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A21" s="1" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A22" s="1" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="1" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A23" s="1" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="1" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A24" s="1" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="1" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A25" s="1" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="1" t="s">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A26" s="1" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
-      <c r="A26" s="1" t="s">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A27" s="1" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="1" t="s">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A28" s="1" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="1" t="s">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A29" s="1" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="1" t="s">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A30" s="1" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="1" t="s">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A31" s="1" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="1" t="s">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A32" s="1" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="1" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A33" s="1" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="1" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A34" s="1" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="1" t="s">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A35" s="1" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="1" t="s">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A36" s="1" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="1" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A37" s="1" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="1" t="s">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A38" s="1" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="1" t="s">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A39" s="1" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="1" t="s">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A40" s="1" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="1" t="s">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A41" s="1" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="1" t="s">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A42" s="1" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="1" t="s">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A43" s="1" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="1" t="s">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A44" s="1" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
-      <c r="A44" s="1" t="s">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A45" s="1" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A46" s="1" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
-      <c r="A46" s="1" t="s">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A47" s="1" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
-      <c r="A47" s="1" t="s">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A48" s="1" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="1" t="s">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A49" s="1" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
-      <c r="A49" s="1" t="s">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A50" s="1" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
-      <c r="A50" s="1" t="s">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A51" s="1" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
-      <c r="A51" s="1" t="s">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A52" s="1" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
-      <c r="A52" s="1" t="s">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A53" s="1" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
-      <c r="A53" s="1" t="s">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A54" s="1" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
-      <c r="A54" s="1" t="s">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A55" s="1" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
-      <c r="A55" s="1" t="s">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A56" s="1" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
-      <c r="A56" s="1" t="s">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A57" s="1" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
-      <c r="A57" s="1" t="s">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A58" s="1" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
-      <c r="A58" s="1" t="s">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A59" s="1" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
-      <c r="A59" s="1" t="s">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A60" s="1" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
-      <c r="A60" s="1" t="s">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A61" s="1" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
-      <c r="A61" s="1" t="s">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A62" s="1" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="62" spans="1:1">
-      <c r="A62" s="1" t="s">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A63" s="1" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
-      <c r="A63" s="1" t="s">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A64" s="1" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="64" spans="1:1">
-      <c r="A64" s="1" t="s">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A65" s="1" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="65" spans="1:1">
-      <c r="A65" s="1" t="s">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A66" s="1" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="66" spans="1:1">
-      <c r="A66" s="1" t="s">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A67" s="1" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="67" spans="1:1">
-      <c r="A67" s="1" t="s">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A68" s="1" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="68" spans="1:1">
-      <c r="A68" s="1" t="s">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A69" s="1" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="69" spans="1:1">
-      <c r="A69" s="1" t="s">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A70" s="1" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="70" spans="1:1">
-      <c r="A70" s="1" t="s">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A71" s="1" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="71" spans="1:1">
-      <c r="A71" s="1" t="s">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A72" s="1" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="72" spans="1:1">
-      <c r="A72" s="1" t="s">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A73" s="1" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="73" spans="1:1">
-      <c r="A73" s="1" t="s">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A74" s="1" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="74" spans="1:1">
-      <c r="A74" s="1" t="s">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A75" s="1" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="75" spans="1:1">
-      <c r="A75" s="1" t="s">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A76" s="1" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="76" spans="1:1">
-      <c r="A76" s="1" t="s">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A77" s="1" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="77" spans="1:1">
-      <c r="A77" s="1" t="s">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A78" s="1" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="78" spans="1:1">
-      <c r="A78" s="1" t="s">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A79" s="1" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="79" spans="1:1">
-      <c r="A79" s="1" t="s">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A80" s="1" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="80" spans="1:1">
-      <c r="A80" s="1" t="s">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A81" s="1" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="81" spans="1:1">
-      <c r="A81" s="1" t="s">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A82" s="1" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="82" spans="1:1">
-      <c r="A82" s="1" t="s">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A83" s="1" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="83" spans="1:1">
-      <c r="A83" s="1" t="s">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A84" s="1" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="84" spans="1:1">
-      <c r="A84" s="1" t="s">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A85" s="1" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="85" spans="1:1">
-      <c r="A85" s="1" t="s">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A86" s="1" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="86" spans="1:1">
-      <c r="A86" s="1" t="s">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A87" s="1" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="87" spans="1:1">
-      <c r="A87" s="1" t="s">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A88" s="1" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="88" spans="1:1">
-      <c r="A88" s="1" t="s">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A89" s="1" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="89" spans="1:1">
-      <c r="A89" s="1" t="s">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A90" s="1" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="90" spans="1:1">
-      <c r="A90" s="1" t="s">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A91" s="1" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="91" spans="1:1">
-      <c r="A91" s="1" t="s">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A92" s="1" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="92" spans="1:1">
-      <c r="A92" s="1" t="s">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A93" s="1" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="93" spans="1:1">
-      <c r="A93" s="1" t="s">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A94" s="1" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="94" spans="1:1">
-      <c r="A94" s="1" t="s">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A95" s="1" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="95" spans="1:1">
-      <c r="A95" s="1" t="s">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A96" s="1" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="96" spans="1:1">
-      <c r="A96" s="1" t="s">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A97" s="1" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="97" spans="1:1">
-      <c r="A97" s="1" t="s">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A98" s="1" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="98" spans="1:1">
-      <c r="A98" s="1" t="s">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A99" s="1" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="99" spans="1:1">
-      <c r="A99" s="1" t="s">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A100" s="1" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="100" spans="1:1">
-      <c r="A100" s="1" t="s">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A101" s="1" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="101" spans="1:1">
-      <c r="A101" s="1" t="s">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A102" s="1" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="102" spans="1:1">
-      <c r="A102" s="1" t="s">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A103" s="1" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="103" spans="1:1">
-      <c r="A103" s="1" t="s">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A104" s="1" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="104" spans="1:1">
-      <c r="A104" s="1" t="s">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A105" s="1" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="105" spans="1:1">
-      <c r="A105" s="1" t="s">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A106" s="1" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="106" spans="1:1">
-      <c r="A106" s="1" t="s">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A107" s="1" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="107" spans="1:1">
-      <c r="A107" s="1" t="s">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A108" s="1" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="108" spans="1:1">
-      <c r="A108" s="1" t="s">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A109" s="1" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="109" spans="1:1">
-      <c r="A109" s="1" t="s">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A110" s="1" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="110" spans="1:1">
-      <c r="A110" s="1" t="s">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A111" s="1" t="s">
         <v>624</v>
       </c>
     </row>
-    <row r="111" spans="1:1">
-      <c r="A111" s="1" t="s">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A112" s="1" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="112" spans="1:1">
-      <c r="A112" s="1" t="s">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A113" s="1" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="113" spans="1:1">
-      <c r="A113" s="1" t="s">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A114" s="1" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="114" spans="1:1">
-      <c r="A114" s="1" t="s">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A115" s="1" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="115" spans="1:1">
-      <c r="A115" s="1" t="s">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A116" s="1" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="116" spans="1:1">
-      <c r="A116" s="1" t="s">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A117" s="1" t="s">
         <v>630</v>
       </c>
     </row>
-    <row r="117" spans="1:1">
-      <c r="A117" s="1" t="s">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A118" s="1" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="118" spans="1:1">
-      <c r="A118" s="1" t="s">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A119" s="1" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="119" spans="1:1">
-      <c r="A119" s="1" t="s">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A120" s="1" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="120" spans="1:1">
-      <c r="A120" s="1" t="s">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A121" s="1" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="121" spans="1:1">
-      <c r="A121" s="1" t="s">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A122" s="1" t="s">
         <v>635</v>
       </c>
     </row>
-    <row r="122" spans="1:1">
-      <c r="A122" s="1" t="s">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A123" s="1" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="123" spans="1:1">
-      <c r="A123" s="1" t="s">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A124" s="1" t="s">
         <v>637</v>
       </c>
     </row>
-    <row r="124" spans="1:1">
-      <c r="A124" s="1" t="s">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A125" s="1" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="125" spans="1:1">
-      <c r="A125" s="1" t="s">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A126" s="1" t="s">
         <v>639</v>
       </c>
     </row>
-    <row r="126" spans="1:1">
-      <c r="A126" s="1" t="s">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A127" s="1" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="127" spans="1:1">
-      <c r="A127" s="1" t="s">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A128" s="1" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="128" spans="1:1">
-      <c r="A128" s="1" t="s">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A129" s="1" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="129" spans="1:1">
-      <c r="A129" s="1" t="s">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A130" s="1" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="130" spans="1:1">
-      <c r="A130" s="1" t="s">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A131" s="1" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="131" spans="1:1">
-      <c r="A131" s="1" t="s">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A132" s="1" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="132" spans="1:1">
-      <c r="A132" s="1" t="s">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A133" s="1" t="s">
         <v>646</v>
       </c>
     </row>
-    <row r="133" spans="1:1">
-      <c r="A133" s="1" t="s">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A134" s="1" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="134" spans="1:1">
-      <c r="A134" s="1" t="s">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A135" s="1" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="135" spans="1:1">
-      <c r="A135" s="1" t="s">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A136" s="1" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="136" spans="1:1">
-      <c r="A136" s="1" t="s">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A137" s="1" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="137" spans="1:1">
-      <c r="A137" s="1" t="s">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A138" s="1" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="138" spans="1:1">
-      <c r="A138" s="1" t="s">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A139" s="1" t="s">
         <v>652</v>
       </c>
     </row>
-    <row r="139" spans="1:1">
-      <c r="A139" s="1" t="s">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A140" s="1" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="140" spans="1:1">
-      <c r="A140" s="1" t="s">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A141" s="1" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="141" spans="1:1">
-      <c r="A141" s="1" t="s">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A142" s="1" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="142" spans="1:1">
-      <c r="A142" s="1" t="s">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A143" s="1" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="143" spans="1:1">
-      <c r="A143" s="1" t="s">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A144" s="1" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="144" spans="1:1">
-      <c r="A144" s="1" t="s">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A145" s="1" t="s">
         <v>658</v>
       </c>
     </row>
-    <row r="145" spans="1:1">
-      <c r="A145" s="1" t="s">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A146" s="1" t="s">
         <v>659</v>
       </c>
     </row>
-    <row r="146" spans="1:1">
-      <c r="A146" s="1" t="s">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A147" s="1" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="147" spans="1:1">
-      <c r="A147" s="1" t="s">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A148" s="1" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="148" spans="1:1">
-      <c r="A148" s="1" t="s">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A149" s="1" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="149" spans="1:1">
-      <c r="A149" s="1" t="s">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A150" s="1" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="150" spans="1:1">
-      <c r="A150" s="1" t="s">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A151" s="1" t="s">
         <v>664</v>
       </c>
     </row>
-    <row r="151" spans="1:1">
-      <c r="A151" s="1" t="s">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A152" s="1" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="152" spans="1:1">
-      <c r="A152" s="1" t="s">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A153" s="1" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="153" spans="1:1">
-      <c r="A153" s="1" t="s">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A154" s="1" t="s">
         <v>667</v>
       </c>
     </row>
-    <row r="154" spans="1:1">
-      <c r="A154" s="1" t="s">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A155" s="1" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="155" spans="1:1">
-      <c r="A155" s="1" t="s">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A156" s="1" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="156" spans="1:1">
-      <c r="A156" s="1" t="s">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A157" s="1" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="157" spans="1:1">
-      <c r="A157" s="1" t="s">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A158" s="1" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="158" spans="1:1">
-      <c r="A158" s="1" t="s">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A159" s="1" t="s">
         <v>672</v>
       </c>
     </row>
-    <row r="159" spans="1:1">
-      <c r="A159" s="1" t="s">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A160" s="1" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="160" spans="1:1">
-      <c r="A160" s="1" t="s">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A161" s="1" t="s">
         <v>674</v>
       </c>
     </row>
-    <row r="161" spans="1:1">
-      <c r="A161" s="1" t="s">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A162" s="1" t="s">
         <v>675</v>
       </c>
     </row>
-    <row r="162" spans="1:1">
-      <c r="A162" s="1" t="s">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A163" s="1" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="163" spans="1:1">
-      <c r="A163" s="1" t="s">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A164" s="1" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="164" spans="1:1">
-      <c r="A164" s="1" t="s">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A165" s="1" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="165" spans="1:1">
-      <c r="A165" s="1" t="s">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A166" s="1" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="166" spans="1:1">
-      <c r="A166" s="1" t="s">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A167" s="1" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="167" spans="1:1">
-      <c r="A167" s="1" t="s">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A168" s="1" t="s">
         <v>681</v>
       </c>
     </row>
-    <row r="168" spans="1:1">
-      <c r="A168" s="1" t="s">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A169" s="1" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="169" spans="1:1">
-      <c r="A169" s="1" t="s">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A170" s="1" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="170" spans="1:1">
-      <c r="A170" s="1" t="s">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A171" s="1" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="171" spans="1:1">
-      <c r="A171" s="1" t="s">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A172" s="1" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="172" spans="1:1">
-      <c r="A172" s="1" t="s">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A173" s="1" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="173" spans="1:1">
-      <c r="A173" s="1" t="s">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A174" s="1" t="s">
         <v>687</v>
       </c>
     </row>
-    <row r="174" spans="1:1">
-      <c r="A174" s="1" t="s">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A175" s="1" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="175" spans="1:1">
-      <c r="A175" s="1" t="s">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A176" s="1" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="176" spans="1:1">
-      <c r="A176" s="1" t="s">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A177" s="1" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="177" spans="1:1">
-      <c r="A177" s="1" t="s">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A178" s="1" t="s">
         <v>691</v>
-      </c>
-    </row>
-    <row r="178" spans="1:1">
-      <c r="A178" s="1" t="s">
-        <v>692</v>
       </c>
     </row>
   </sheetData>
@@ -10698,20 +10718,20 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A2:P49"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="18.5" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A2" s="54" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A3" s="58" t="s">
         <v>406</v>
       </c>
@@ -10728,15 +10748,15 @@
         <v>410</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A4" s="58"/>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A5" s="59" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A7" s="58" t="s">
         <v>413</v>
       </c>
@@ -10777,7 +10797,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>426</v>
       </c>
@@ -10818,7 +10838,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.15">
       <c r="B9" t="s">
         <v>435</v>
       </c>
@@ -10841,7 +10861,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.15">
       <c r="D10" t="s">
         <v>441</v>
       </c>
@@ -10852,7 +10872,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.15">
       <c r="D11" t="s">
         <v>444</v>
       </c>
@@ -10863,7 +10883,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.15">
       <c r="D12" t="s">
         <v>447</v>
       </c>
@@ -10871,7 +10891,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.15">
       <c r="D13" t="s">
         <v>449</v>
       </c>
@@ -10879,7 +10899,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.15">
       <c r="D14" t="s">
         <v>451</v>
       </c>
@@ -10887,12 +10907,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.15">
       <c r="D15" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>426</v>
       </c>
@@ -10900,7 +10920,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>427</v>
       </c>
@@ -10908,7 +10928,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>435</v>
       </c>
@@ -10916,7 +10936,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>428</v>
       </c>
@@ -10924,7 +10944,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>436</v>
       </c>
@@ -10932,7 +10952,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>429</v>
       </c>
@@ -10940,7 +10960,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>437</v>
       </c>
@@ -10948,7 +10968,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>441</v>
       </c>
@@ -10956,7 +10976,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="25" spans="1:16">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>444</v>
       </c>
@@ -10964,7 +10984,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="26" spans="1:16">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>447</v>
       </c>
@@ -10972,7 +10992,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="27" spans="1:16">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>449</v>
       </c>
@@ -10980,7 +11000,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="28" spans="1:16">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>451</v>
       </c>
@@ -10988,7 +11008,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="29" spans="1:16">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
         <v>453</v>
       </c>
@@ -10996,7 +11016,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="30" spans="1:16">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
         <v>430</v>
       </c>
@@ -11046,7 +11066,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="31" spans="1:16">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
         <v>438</v>
       </c>
@@ -11054,7 +11074,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="32" spans="1:16">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
         <v>431</v>
       </c>
@@ -11062,7 +11082,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
         <v>439</v>
       </c>
@@ -11070,7 +11090,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
         <v>442</v>
       </c>
@@ -11078,7 +11098,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
         <v>445</v>
       </c>
@@ -11086,7 +11106,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
         <v>448</v>
       </c>
@@ -11094,7 +11114,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
         <v>450</v>
       </c>
@@ -11102,7 +11122,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
         <v>452</v>
       </c>
@@ -11110,7 +11130,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
         <v>432</v>
       </c>
@@ -11121,7 +11141,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A40" t="s">
         <v>440</v>
       </c>
@@ -11156,7 +11176,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A41" t="s">
         <v>443</v>
       </c>
@@ -11167,7 +11187,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A42" t="s">
         <v>446</v>
       </c>
@@ -11175,7 +11195,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A43" s="58" t="s">
         <v>489</v>
       </c>
@@ -11186,7 +11206,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A44" s="58" t="s">
         <v>490</v>
       </c>
@@ -11197,7 +11217,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A45" t="s">
         <v>433</v>
       </c>
@@ -11206,7 +11226,7 @@
       </c>
       <c r="H45" s="58"/>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A46" t="s">
         <v>434</v>
       </c>
@@ -11214,7 +11234,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A47" t="s">
         <v>423</v>
       </c>
@@ -11222,7 +11242,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A48" t="s">
         <v>424</v>
       </c>
@@ -11230,7 +11250,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A49" t="s">
         <v>425</v>
       </c>
